--- a/research/traditional_assets/database/data/morocco/morocco_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_r_e_i_t.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08429349859288182</v>
+        <v>0.08405435939738461</v>
       </c>
       <c r="C2">
-        <v>96.32865337173214</v>
+        <v>95.95763172576211</v>
       </c>
       <c r="D2">
-        <v>96.13665337173215</v>
+        <v>96.73763172576211</v>
       </c>
       <c r="E2">
-        <v>-17.2</v>
+        <v>-16.228</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9720000000000001</v>
       </c>
       <c r="G2">
         <v>0.192</v>
@@ -1451,28 +1451,28 @@
         <v>1.815</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0488916</v>
       </c>
       <c r="N2">
-        <v>1.815</v>
+        <v>1.7661084</v>
       </c>
       <c r="O2">
-        <v>0.5807999999999999</v>
+        <v>0.5651546879999999</v>
       </c>
       <c r="P2">
-        <v>1.2342</v>
+        <v>1.200953712</v>
       </c>
       <c r="Q2">
-        <v>4.694199999999999</v>
+        <v>4.660953712</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08429349859288182</v>
+        <v>0.08455789838119657</v>
       </c>
       <c r="T2">
-        <v>0.5016993284768603</v>
+        <v>0.5051453440663983</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>37.1229413641607</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08405435939738461</v>
+        <v>0.08381522020188739</v>
       </c>
       <c r="C3">
-        <v>95.95763172576211</v>
+        <v>95.59417112925229</v>
       </c>
       <c r="D3">
-        <v>96.73763172576211</v>
+        <v>97.3461711292523</v>
       </c>
       <c r="E3">
-        <v>-16.228</v>
+        <v>-15.256</v>
       </c>
       <c r="F3">
-        <v>0.9720000000000001</v>
+        <v>1.944</v>
       </c>
       <c r="G3">
         <v>0.192</v>
@@ -1533,28 +1533,28 @@
         <v>1.815</v>
       </c>
       <c r="M3">
-        <v>0.0488916</v>
+        <v>0.0977832</v>
       </c>
       <c r="N3">
-        <v>1.7661084</v>
+        <v>1.717216799999999</v>
       </c>
       <c r="O3">
-        <v>0.5651546879999999</v>
+        <v>0.5495093759999998</v>
       </c>
       <c r="P3">
-        <v>1.200953712</v>
+        <v>1.167707424</v>
       </c>
       <c r="Q3">
-        <v>4.660953712</v>
+        <v>4.627707424</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08455789838119657</v>
+        <v>0.08482769408355856</v>
       </c>
       <c r="T3">
-        <v>0.5051453440663983</v>
+        <v>0.5086616865047023</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>37.1229413641607</v>
+        <v>18.56147068208035</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08381522020188739</v>
+        <v>0.08360668100639015</v>
       </c>
       <c r="C4">
-        <v>95.59417112925229</v>
+        <v>95.15912628298821</v>
       </c>
       <c r="D4">
-        <v>97.3461711292523</v>
+        <v>97.88312628298821</v>
       </c>
       <c r="E4">
-        <v>-15.256</v>
+        <v>-14.284</v>
       </c>
       <c r="F4">
-        <v>1.944</v>
+        <v>2.916</v>
       </c>
       <c r="G4">
         <v>0.192</v>
@@ -1615,45 +1615,45 @@
         <v>1.815</v>
       </c>
       <c r="M4">
-        <v>0.0977832</v>
+        <v>0.1510488</v>
       </c>
       <c r="N4">
-        <v>1.717216799999999</v>
+        <v>1.6639512</v>
       </c>
       <c r="O4">
-        <v>0.5495093759999998</v>
+        <v>0.5324643839999998</v>
       </c>
       <c r="P4">
-        <v>1.167707424</v>
+        <v>1.131486816</v>
       </c>
       <c r="Q4">
-        <v>4.627707424</v>
+        <v>4.591486816</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08482769408355856</v>
+        <v>0.08510305258390738</v>
       </c>
       <c r="T4">
-        <v>0.5086616865047023</v>
+        <v>0.512250530848951</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.32</v>
       </c>
       <c r="W4">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>18.56147068208035</v>
+        <v>12.01598423820646</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08360668100639015</v>
+        <v>0.08342398181089294</v>
       </c>
       <c r="C5">
-        <v>95.15912628298821</v>
+        <v>94.66243930313951</v>
       </c>
       <c r="D5">
-        <v>97.88312628298821</v>
+        <v>98.35843930313952</v>
       </c>
       <c r="E5">
-        <v>-14.284</v>
+        <v>-13.312</v>
       </c>
       <c r="F5">
-        <v>2.916</v>
+        <v>3.888</v>
       </c>
       <c r="G5">
         <v>0.192</v>
@@ -1697,45 +1697,45 @@
         <v>1.815</v>
       </c>
       <c r="M5">
-        <v>0.1510488</v>
+        <v>0.208008</v>
       </c>
       <c r="N5">
-        <v>1.6639512</v>
+        <v>1.606992</v>
       </c>
       <c r="O5">
-        <v>0.5324643839999998</v>
+        <v>0.5142374399999998</v>
       </c>
       <c r="P5">
-        <v>1.131486816</v>
+        <v>1.09275456</v>
       </c>
       <c r="Q5">
-        <v>4.591486816</v>
+        <v>4.552754559999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08510305258390738</v>
+        <v>0.08538414771968014</v>
       </c>
       <c r="T5">
-        <v>0.512250530848951</v>
+        <v>0.5159141427837046</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.32</v>
       </c>
       <c r="W5">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>12.01598423820646</v>
+        <v>8.72562593746394</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08342398181089294</v>
+        <v>0.08323380261539573</v>
       </c>
       <c r="C6">
-        <v>94.66243930313951</v>
+        <v>94.1901408442632</v>
       </c>
       <c r="D6">
-        <v>98.35843930313952</v>
+        <v>98.8581408442632</v>
       </c>
       <c r="E6">
-        <v>-13.312</v>
+        <v>-12.34</v>
       </c>
       <c r="F6">
-        <v>3.888</v>
+        <v>4.86</v>
       </c>
       <c r="G6">
         <v>0.192</v>
@@ -1779,45 +1779,45 @@
         <v>1.815</v>
       </c>
       <c r="M6">
-        <v>0.208008</v>
+        <v>0.263898</v>
       </c>
       <c r="N6">
-        <v>1.606992</v>
+        <v>1.551102</v>
       </c>
       <c r="O6">
-        <v>0.5142374399999998</v>
+        <v>0.4963526399999998</v>
       </c>
       <c r="P6">
-        <v>1.09275456</v>
+        <v>1.05474936</v>
       </c>
       <c r="Q6">
-        <v>4.552754559999999</v>
+        <v>4.51474936</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08538414771968014</v>
+        <v>0.08567116064778497</v>
       </c>
       <c r="T6">
-        <v>0.5159141427837046</v>
+        <v>0.519654883390769</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.32</v>
       </c>
       <c r="W6">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.72562593746394</v>
+        <v>6.877657276675077</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08323380261539573</v>
+        <v>0.0830626634198985</v>
       </c>
       <c r="C7">
-        <v>94.1901408442632</v>
+        <v>93.67217448382866</v>
       </c>
       <c r="D7">
-        <v>98.8581408442632</v>
+        <v>99.31217448382866</v>
       </c>
       <c r="E7">
-        <v>-12.34</v>
+        <v>-11.368</v>
       </c>
       <c r="F7">
-        <v>4.86</v>
+        <v>5.832000000000001</v>
       </c>
       <c r="G7">
         <v>0.192</v>
@@ -1861,45 +1861,45 @@
         <v>1.815</v>
       </c>
       <c r="M7">
-        <v>0.263898</v>
+        <v>0.3225096000000001</v>
       </c>
       <c r="N7">
-        <v>1.551102</v>
+        <v>1.492490399999999</v>
       </c>
       <c r="O7">
-        <v>0.4963526399999998</v>
+        <v>0.4775969279999998</v>
       </c>
       <c r="P7">
-        <v>1.05474936</v>
+        <v>1.014893472</v>
       </c>
       <c r="Q7">
-        <v>4.51474936</v>
+        <v>4.474893472</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08567116064778497</v>
+        <v>0.08596428023393457</v>
       </c>
       <c r="T7">
-        <v>0.519654883390769</v>
+        <v>0.5234752142235155</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.32</v>
       </c>
       <c r="W7">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.877657276675077</v>
+        <v>5.627739453337201</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08306266341989849</v>
+        <v>0.08285752422440128</v>
       </c>
       <c r="C8">
-        <v>93.6721744838287</v>
+        <v>93.24993650930355</v>
       </c>
       <c r="D8">
-        <v>99.3121744838287</v>
+        <v>99.86193650930356</v>
       </c>
       <c r="E8">
-        <v>-11.368</v>
+        <v>-10.396</v>
       </c>
       <c r="F8">
-        <v>5.832</v>
+        <v>6.803999999999999</v>
       </c>
       <c r="G8">
         <v>0.192</v>
@@ -1943,28 +1943,28 @@
         <v>1.815</v>
       </c>
       <c r="M8">
-        <v>0.3225096</v>
+        <v>0.3762612</v>
       </c>
       <c r="N8">
-        <v>1.492490399999999</v>
+        <v>1.438738799999999</v>
       </c>
       <c r="O8">
-        <v>0.4775969279999998</v>
+        <v>0.4603964159999998</v>
       </c>
       <c r="P8">
-        <v>1.014893472</v>
+        <v>0.9783423839999996</v>
       </c>
       <c r="Q8">
-        <v>4.474893472</v>
+        <v>4.438342383999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08596428023393457</v>
+        <v>0.08626370346709815</v>
       </c>
       <c r="T8">
-        <v>0.5234752142235155</v>
+        <v>0.5273777027085792</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.627739453337201</v>
+        <v>4.82377667428903</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08285752422440128</v>
+        <v>0.08278838502890407</v>
       </c>
       <c r="C9">
-        <v>93.24993650930355</v>
+        <v>92.46459980767821</v>
       </c>
       <c r="D9">
-        <v>99.86193650930356</v>
+        <v>100.0485998076782</v>
       </c>
       <c r="E9">
-        <v>-10.396</v>
+        <v>-9.423999999999999</v>
       </c>
       <c r="F9">
-        <v>6.804000000000001</v>
+        <v>7.776000000000001</v>
       </c>
       <c r="G9">
         <v>0.192</v>
@@ -2025,45 +2025,45 @@
         <v>1.815</v>
       </c>
       <c r="M9">
-        <v>0.3762612000000001</v>
+        <v>0.4494528000000001</v>
       </c>
       <c r="N9">
-        <v>1.438738799999999</v>
+        <v>1.3655472</v>
       </c>
       <c r="O9">
-        <v>0.4603964159999998</v>
+        <v>0.4369751039999998</v>
       </c>
       <c r="P9">
-        <v>0.9783423839999996</v>
+        <v>0.9285720959999997</v>
       </c>
       <c r="Q9">
-        <v>4.438342383999999</v>
+        <v>4.388572096</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08626370346709815</v>
+        <v>0.08656963590098267</v>
       </c>
       <c r="T9">
-        <v>0.5273777027085792</v>
+        <v>0.5313650278998399</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V9">
         <v>0.32</v>
       </c>
       <c r="W9">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.823776674289029</v>
+        <v>4.038243837840145</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08278838502890407</v>
+        <v>0.08298580583340684</v>
       </c>
       <c r="C10">
-        <v>92.46459980767821</v>
+        <v>90.96143812862529</v>
       </c>
       <c r="D10">
-        <v>100.0485998076782</v>
+        <v>99.5174381286253</v>
       </c>
       <c r="E10">
-        <v>-9.423999999999999</v>
+        <v>-8.452</v>
       </c>
       <c r="F10">
-        <v>7.776000000000001</v>
+        <v>8.747999999999999</v>
       </c>
       <c r="G10">
         <v>0.192</v>
@@ -2107,45 +2107,45 @@
         <v>1.815</v>
       </c>
       <c r="M10">
-        <v>0.4494528000000001</v>
+        <v>0.5607468</v>
       </c>
       <c r="N10">
-        <v>1.3655472</v>
+        <v>1.2542532</v>
       </c>
       <c r="O10">
-        <v>0.4369751039999998</v>
+        <v>0.4013610239999998</v>
       </c>
       <c r="P10">
-        <v>0.9285720959999997</v>
+        <v>0.8528921759999997</v>
       </c>
       <c r="Q10">
-        <v>4.388572096</v>
+        <v>4.312892176</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08656963590098267</v>
+        <v>0.0868822921246229</v>
       </c>
       <c r="T10">
-        <v>0.5313650278998399</v>
+        <v>0.5354399866117876</v>
       </c>
       <c r="U10">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.039304</v>
+        <v>0.043588</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.038243837840145</v>
+        <v>3.236754984602675</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08298580583340684</v>
+        <v>0.08337090663790962</v>
       </c>
       <c r="C11">
-        <v>90.96143812862529</v>
+        <v>88.96938700623052</v>
       </c>
       <c r="D11">
-        <v>99.5174381286253</v>
+        <v>98.49738700623053</v>
       </c>
       <c r="E11">
-        <v>-8.452</v>
+        <v>-7.48</v>
       </c>
       <c r="F11">
-        <v>8.747999999999999</v>
+        <v>9.719999999999999</v>
       </c>
       <c r="G11">
         <v>0.192</v>
@@ -2189,45 +2189,45 @@
         <v>1.815</v>
       </c>
       <c r="M11">
-        <v>0.5607468</v>
+        <v>0.6988679999999999</v>
       </c>
       <c r="N11">
-        <v>1.2542532</v>
+        <v>1.116131999999999</v>
       </c>
       <c r="O11">
-        <v>0.4013610239999998</v>
+        <v>0.3571622399999999</v>
       </c>
       <c r="P11">
-        <v>0.8528921759999997</v>
+        <v>0.7589697599999996</v>
       </c>
       <c r="Q11">
-        <v>4.312892176</v>
+        <v>4.218969759999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0868822921246229</v>
+        <v>0.08720189626434402</v>
       </c>
       <c r="T11">
-        <v>0.5354399866117876</v>
+        <v>0.5396054999617786</v>
       </c>
       <c r="U11">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.236754984602675</v>
+        <v>2.597056954961452</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08337090663790962</v>
+        <v>0.08357036744241238</v>
       </c>
       <c r="C12">
-        <v>88.96938700623052</v>
+        <v>87.47723405607357</v>
       </c>
       <c r="D12">
-        <v>98.49738700623053</v>
+        <v>97.97723405607358</v>
       </c>
       <c r="E12">
-        <v>-7.479999999999999</v>
+        <v>-6.507999999999999</v>
       </c>
       <c r="F12">
-        <v>9.720000000000001</v>
+        <v>10.692</v>
       </c>
       <c r="G12">
         <v>0.192</v>
@@ -2271,45 +2271,45 @@
         <v>1.815</v>
       </c>
       <c r="M12">
-        <v>0.698868</v>
+        <v>0.8104536000000001</v>
       </c>
       <c r="N12">
-        <v>1.116131999999999</v>
+        <v>1.004546399999999</v>
       </c>
       <c r="O12">
-        <v>0.3571622399999999</v>
+        <v>0.3214548479999998</v>
       </c>
       <c r="P12">
-        <v>0.7589697599999996</v>
+        <v>0.6830915519999995</v>
       </c>
       <c r="Q12">
-        <v>4.218969759999999</v>
+        <v>4.143091552</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08720189626434402</v>
+        <v>0.08752868251956447</v>
       </c>
       <c r="T12">
-        <v>0.5396054999617786</v>
+        <v>0.5438646203533424</v>
       </c>
       <c r="U12">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.597056954961451</v>
+        <v>2.239486628228931</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08357036744241238</v>
+        <v>0.08350462824691517</v>
       </c>
       <c r="C13">
-        <v>87.47723405607357</v>
+        <v>86.67606041992762</v>
       </c>
       <c r="D13">
-        <v>97.97723405607358</v>
+        <v>98.14806041992763</v>
       </c>
       <c r="E13">
-        <v>-6.507999999999999</v>
+        <v>-5.536</v>
       </c>
       <c r="F13">
-        <v>10.692</v>
+        <v>11.664</v>
       </c>
       <c r="G13">
         <v>0.192</v>
@@ -2353,28 +2353,28 @@
         <v>1.815</v>
       </c>
       <c r="M13">
-        <v>0.8104536000000001</v>
+        <v>0.8841312</v>
       </c>
       <c r="N13">
-        <v>1.004546399999999</v>
+        <v>0.9308687999999995</v>
       </c>
       <c r="O13">
-        <v>0.3214548479999998</v>
+        <v>0.2978780159999999</v>
       </c>
       <c r="P13">
-        <v>0.6830915519999995</v>
+        <v>0.6329907839999996</v>
       </c>
       <c r="Q13">
-        <v>4.143091552</v>
+        <v>4.092990783999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08752868251956447</v>
+        <v>0.08786289573513087</v>
       </c>
       <c r="T13">
-        <v>0.5438646203533424</v>
+        <v>0.5482205389356237</v>
       </c>
       <c r="U13">
         <v>0.07580000000000001</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.239486628228931</v>
+        <v>2.052862742543188</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08350462824691517</v>
+        <v>0.08469416905141795</v>
       </c>
       <c r="C14">
-        <v>86.67606041992762</v>
+        <v>82.70229625836488</v>
       </c>
       <c r="D14">
-        <v>98.14806041992763</v>
+        <v>95.14629625836488</v>
       </c>
       <c r="E14">
-        <v>-5.536</v>
+        <v>-4.563999999999998</v>
       </c>
       <c r="F14">
-        <v>11.664</v>
+        <v>12.636</v>
       </c>
       <c r="G14">
         <v>0.192</v>
@@ -2435,45 +2435,45 @@
         <v>1.815</v>
       </c>
       <c r="M14">
-        <v>0.8841312</v>
+        <v>1.13724</v>
       </c>
       <c r="N14">
-        <v>0.9308687999999995</v>
+        <v>0.6777599999999995</v>
       </c>
       <c r="O14">
-        <v>0.2978780159999999</v>
+        <v>0.2168831999999998</v>
       </c>
       <c r="P14">
-        <v>0.6329907839999996</v>
+        <v>0.4608767999999996</v>
       </c>
       <c r="Q14">
-        <v>4.092990783999999</v>
+        <v>3.920876799999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08786289573513087</v>
+        <v>0.08820479201312408</v>
       </c>
       <c r="T14">
-        <v>0.5482205389356237</v>
+        <v>0.5526765935772677</v>
       </c>
       <c r="U14">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V14">
         <v>0.32</v>
       </c>
       <c r="W14">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.052862742543188</v>
+        <v>1.595969188561781</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08469416905141795</v>
+        <v>0.09089136069476271</v>
       </c>
       <c r="C15">
-        <v>82.70229625836488</v>
+        <v>68.65373740135905</v>
       </c>
       <c r="D15">
-        <v>95.14629625836488</v>
+        <v>82.06973740135906</v>
       </c>
       <c r="E15">
-        <v>-4.563999999999998</v>
+        <v>-3.591999999999997</v>
       </c>
       <c r="F15">
-        <v>12.636</v>
+        <v>13.608</v>
       </c>
       <c r="G15">
         <v>0.192</v>
@@ -2517,45 +2517,45 @@
         <v>1.815</v>
       </c>
       <c r="M15">
-        <v>1.13724</v>
+        <v>1.9976544</v>
       </c>
       <c r="N15">
-        <v>0.6777599999999995</v>
+        <v>-0.182654400000001</v>
       </c>
       <c r="O15">
-        <v>0.2168831999999998</v>
+        <v>-0.05844940800000032</v>
       </c>
       <c r="P15">
-        <v>0.4608767999999996</v>
+        <v>-0.1242049920000007</v>
       </c>
       <c r="Q15">
-        <v>3.920876799999999</v>
+        <v>3.335795007999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08820479201312408</v>
+        <v>0.08873798760085816</v>
       </c>
       <c r="T15">
-        <v>0.5526765935772677</v>
+        <v>0.5596259195177912</v>
       </c>
       <c r="U15">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.32</v>
+        <v>0.2907409810225431</v>
       </c>
       <c r="W15">
-        <v>0.06119999999999999</v>
+        <v>0.1041192239858907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y15">
-        <v>1.595969188561781</v>
+        <v>0.9085655656954471</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09089136069476271</v>
+        <v>0.09190136069476271</v>
       </c>
       <c r="C16">
-        <v>68.65373740135905</v>
+        <v>65.88373331804816</v>
       </c>
       <c r="D16">
-        <v>82.06973740135906</v>
+        <v>80.27173331804816</v>
       </c>
       <c r="E16">
-        <v>-3.591999999999997</v>
+        <v>-2.619999999999997</v>
       </c>
       <c r="F16">
-        <v>13.608</v>
+        <v>14.58</v>
       </c>
       <c r="G16">
         <v>0.192</v>
@@ -2599,37 +2599,37 @@
         <v>1.815</v>
       </c>
       <c r="M16">
-        <v>1.9976544</v>
+        <v>2.140344000000001</v>
       </c>
       <c r="N16">
-        <v>-0.182654400000001</v>
+        <v>-0.3253440000000012</v>
       </c>
       <c r="O16">
-        <v>-0.05844940800000032</v>
+        <v>-0.1041100800000004</v>
       </c>
       <c r="P16">
-        <v>-0.1242049920000007</v>
+        <v>-0.2212339200000008</v>
       </c>
       <c r="Q16">
-        <v>3.335795007999999</v>
+        <v>3.238766079999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08873798760085816</v>
+        <v>0.08924314039616238</v>
       </c>
       <c r="T16">
-        <v>0.5596259195177912</v>
+        <v>0.5662097538650593</v>
       </c>
       <c r="U16">
         <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.2907409810225431</v>
+        <v>0.2713582489543735</v>
       </c>
       <c r="W16">
-        <v>0.1041192239858907</v>
+        <v>0.106964609053498</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.9085655656954471</v>
+        <v>0.8479945279824173</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09190136069476271</v>
+        <v>0.1019727191600603</v>
       </c>
       <c r="C17">
-        <v>65.88373331804816</v>
+        <v>50.51959754528578</v>
       </c>
       <c r="D17">
-        <v>80.27173331804816</v>
+        <v>65.87959754528579</v>
       </c>
       <c r="E17">
-        <v>-2.619999999999999</v>
+        <v>-1.647999999999998</v>
       </c>
       <c r="F17">
-        <v>14.58</v>
+        <v>15.552</v>
       </c>
       <c r="G17">
         <v>0.192</v>
@@ -2681,45 +2681,45 @@
         <v>1.815</v>
       </c>
       <c r="M17">
-        <v>2.140344</v>
+        <v>3.122841600000001</v>
       </c>
       <c r="N17">
-        <v>-0.3253440000000007</v>
+        <v>-1.307841600000001</v>
       </c>
       <c r="O17">
-        <v>-0.1041100800000002</v>
+        <v>-0.4185093120000004</v>
       </c>
       <c r="P17">
-        <v>-0.2212339200000005</v>
+        <v>-0.8893322880000007</v>
       </c>
       <c r="Q17">
-        <v>3.23876608</v>
+        <v>2.570667711999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08924314039616238</v>
+        <v>0.09026193785956625</v>
       </c>
       <c r="T17">
-        <v>0.5662097538650592</v>
+        <v>0.5794881001294379</v>
       </c>
       <c r="U17">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.2713582489543736</v>
+        <v>0.1859844572327971</v>
       </c>
       <c r="W17">
-        <v>0.106964609053498</v>
+        <v>0.1634543209876543</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y17">
-        <v>0.8479945279824175</v>
+        <v>0.5812014288524909</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1019727191600603</v>
+        <v>0.1035227191600604</v>
       </c>
       <c r="C18">
-        <v>50.51959754528578</v>
+        <v>47.77856487182419</v>
       </c>
       <c r="D18">
-        <v>65.87959754528579</v>
+        <v>64.1105648718242</v>
       </c>
       <c r="E18">
-        <v>-1.647999999999998</v>
+        <v>-0.6759999999999984</v>
       </c>
       <c r="F18">
-        <v>15.552</v>
+        <v>16.524</v>
       </c>
       <c r="G18">
         <v>0.192</v>
@@ -2763,37 +2763,37 @@
         <v>1.815</v>
       </c>
       <c r="M18">
-        <v>3.122841600000001</v>
+        <v>3.3180192</v>
       </c>
       <c r="N18">
-        <v>-1.307841600000001</v>
+        <v>-1.503019200000001</v>
       </c>
       <c r="O18">
-        <v>-0.4185093120000004</v>
+        <v>-0.4809661440000002</v>
       </c>
       <c r="P18">
-        <v>-0.8893322880000007</v>
+        <v>-1.022053056000001</v>
       </c>
       <c r="Q18">
-        <v>2.570667711999999</v>
+        <v>2.437946943999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09026193785956625</v>
+        <v>0.09079762385787429</v>
       </c>
       <c r="T18">
-        <v>0.5794881001294379</v>
+        <v>0.5864698844683468</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1859844572327971</v>
+        <v>0.1750441950426326</v>
       </c>
       <c r="W18">
-        <v>0.1634543209876543</v>
+        <v>0.1656511256354394</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.5812014288524909</v>
+        <v>0.5470131095082269</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1035227191600604</v>
+        <v>0.1050727191600604</v>
       </c>
       <c r="C19">
-        <v>47.77856487182419</v>
+        <v>45.13005370514421</v>
       </c>
       <c r="D19">
-        <v>64.1105648718242</v>
+        <v>62.43405370514422</v>
       </c>
       <c r="E19">
-        <v>-0.6759999999999984</v>
+        <v>0.2960000000000029</v>
       </c>
       <c r="F19">
-        <v>16.524</v>
+        <v>17.496</v>
       </c>
       <c r="G19">
         <v>0.192</v>
@@ -2845,37 +2845,37 @@
         <v>1.815</v>
       </c>
       <c r="M19">
-        <v>3.3180192</v>
+        <v>3.513196800000001</v>
       </c>
       <c r="N19">
-        <v>-1.503019200000001</v>
+        <v>-1.698196800000001</v>
       </c>
       <c r="O19">
-        <v>-0.4809661440000002</v>
+        <v>-0.5434229760000003</v>
       </c>
       <c r="P19">
-        <v>-1.022053056000001</v>
+        <v>-1.154773824000001</v>
       </c>
       <c r="Q19">
-        <v>2.437946943999999</v>
+        <v>2.305226175999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09079762385787429</v>
+        <v>0.09134637536833617</v>
       </c>
       <c r="T19">
-        <v>0.5864698844683468</v>
+        <v>0.5936219562301559</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.1750441950426326</v>
+        <v>0.1653195175402641</v>
       </c>
       <c r="W19">
-        <v>0.1656511256354394</v>
+        <v>0.167603840877915</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.5470131095082269</v>
+        <v>0.5166234923133253</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1050727191600604</v>
+        <v>0.1134427423902538</v>
       </c>
       <c r="C20">
-        <v>45.13005370514422</v>
+        <v>36.43254670466968</v>
       </c>
       <c r="D20">
-        <v>62.43405370514422</v>
+        <v>54.70854670466968</v>
       </c>
       <c r="E20">
-        <v>0.2959999999999994</v>
+        <v>1.268000000000001</v>
       </c>
       <c r="F20">
-        <v>17.496</v>
+        <v>18.468</v>
       </c>
       <c r="G20">
         <v>0.192</v>
@@ -2927,45 +2927,45 @@
         <v>1.815</v>
       </c>
       <c r="M20">
-        <v>3.5131968</v>
+        <v>4.3547544</v>
       </c>
       <c r="N20">
-        <v>-1.6981968</v>
+        <v>-2.539754400000001</v>
       </c>
       <c r="O20">
-        <v>-0.5434229760000001</v>
+        <v>-0.8127214080000001</v>
       </c>
       <c r="P20">
-        <v>-1.154773824</v>
+        <v>-1.727032992</v>
       </c>
       <c r="Q20">
-        <v>2.305226176</v>
+        <v>1.732967008</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09134637536833617</v>
+        <v>0.0921185815212705</v>
       </c>
       <c r="T20">
-        <v>0.5936219562301559</v>
+        <v>0.6036863910707058</v>
       </c>
       <c r="U20">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1653195175402642</v>
+        <v>0.1333714709605666</v>
       </c>
       <c r="W20">
-        <v>0.167603840877915</v>
+        <v>0.2043510071474984</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.5166234923133255</v>
+        <v>0.4167858467517708</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1134427423902538</v>
+        <v>0.1153427423902538</v>
       </c>
       <c r="C21">
-        <v>36.43254670466968</v>
+        <v>33.9658366146425</v>
       </c>
       <c r="D21">
-        <v>54.70854670466968</v>
+        <v>53.2138366146425</v>
       </c>
       <c r="E21">
-        <v>1.268000000000001</v>
+        <v>2.240000000000002</v>
       </c>
       <c r="F21">
-        <v>18.468</v>
+        <v>19.44</v>
       </c>
       <c r="G21">
         <v>0.192</v>
@@ -3009,37 +3009,37 @@
         <v>1.815</v>
       </c>
       <c r="M21">
-        <v>4.3547544</v>
+        <v>4.583952000000001</v>
       </c>
       <c r="N21">
-        <v>-2.539754400000001</v>
+        <v>-2.768952000000001</v>
       </c>
       <c r="O21">
-        <v>-0.8127214080000001</v>
+        <v>-0.8860646400000005</v>
       </c>
       <c r="P21">
-        <v>-1.727032992</v>
+        <v>-1.882887360000001</v>
       </c>
       <c r="Q21">
-        <v>1.732967008</v>
+        <v>1.577112639999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0921185815212705</v>
+        <v>0.09269756379028639</v>
       </c>
       <c r="T21">
-        <v>0.6036863910707058</v>
+        <v>0.6112324709590896</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.1333714709605666</v>
+        <v>0.1267028974125383</v>
       </c>
       <c r="W21">
-        <v>0.2043510071474984</v>
+        <v>0.2059234567901235</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4167858467517708</v>
+        <v>0.3959465544141821</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1153427423902538</v>
+        <v>0.1172427423902538</v>
       </c>
       <c r="C22">
-        <v>33.9658366146425</v>
+        <v>31.57862932856814</v>
       </c>
       <c r="D22">
-        <v>53.2138366146425</v>
+        <v>51.79862932856814</v>
       </c>
       <c r="E22">
-        <v>2.240000000000002</v>
+        <v>3.212000000000003</v>
       </c>
       <c r="F22">
-        <v>19.44</v>
+        <v>20.412</v>
       </c>
       <c r="G22">
         <v>0.192</v>
@@ -3091,37 +3091,37 @@
         <v>1.815</v>
       </c>
       <c r="M22">
-        <v>4.583952000000001</v>
+        <v>4.813149600000001</v>
       </c>
       <c r="N22">
-        <v>-2.768952000000001</v>
+        <v>-2.998149600000001</v>
       </c>
       <c r="O22">
-        <v>-0.8860646400000005</v>
+        <v>-0.9594078720000004</v>
       </c>
       <c r="P22">
-        <v>-1.882887360000001</v>
+        <v>-2.038741728000001</v>
       </c>
       <c r="Q22">
-        <v>1.577112639999999</v>
+        <v>1.421258271999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09269756379028639</v>
+        <v>0.0932912038382647</v>
       </c>
       <c r="T22">
-        <v>0.6112324709590896</v>
+        <v>0.6189695908446478</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.1267028974125383</v>
+        <v>0.1206694261071793</v>
       </c>
       <c r="W22">
-        <v>0.2059234567901235</v>
+        <v>0.2073461493239271</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3959465544141821</v>
+        <v>0.3770919565849354</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1172427423902538</v>
+        <v>0.1191427423902538</v>
       </c>
       <c r="C23">
-        <v>31.57862932856814</v>
+        <v>29.2647461030868</v>
       </c>
       <c r="D23">
-        <v>51.79862932856814</v>
+        <v>50.4567461030868</v>
       </c>
       <c r="E23">
-        <v>3.212</v>
+        <v>4.184000000000001</v>
       </c>
       <c r="F23">
-        <v>20.412</v>
+        <v>21.384</v>
       </c>
       <c r="G23">
         <v>0.192</v>
@@ -3173,37 +3173,37 @@
         <v>1.815</v>
       </c>
       <c r="M23">
-        <v>4.8131496</v>
+        <v>5.0423472</v>
       </c>
       <c r="N23">
-        <v>-2.998149600000001</v>
+        <v>-3.227347200000001</v>
       </c>
       <c r="O23">
-        <v>-0.9594078720000002</v>
+        <v>-1.032751104</v>
       </c>
       <c r="P23">
-        <v>-2.038741728</v>
+        <v>-2.194596096000001</v>
       </c>
       <c r="Q23">
-        <v>1.421258272</v>
+        <v>1.265403903999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0932912038382647</v>
+        <v>0.09390006542593476</v>
       </c>
       <c r="T23">
-        <v>0.6189695908446478</v>
+        <v>0.6269050984195791</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.1206694261071793</v>
+        <v>0.1151844521932166</v>
       </c>
       <c r="W23">
-        <v>0.2073461493239271</v>
+        <v>0.2086395061728395</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3770919565849354</v>
+        <v>0.3599514131038021</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1191427423902538</v>
+        <v>0.1210427423902538</v>
       </c>
       <c r="C24">
-        <v>29.2647461030868</v>
+        <v>27.01863228758236</v>
       </c>
       <c r="D24">
-        <v>50.4567461030868</v>
+        <v>49.18263228758236</v>
       </c>
       <c r="E24">
-        <v>4.184000000000001</v>
+        <v>5.156000000000002</v>
       </c>
       <c r="F24">
-        <v>21.384</v>
+        <v>22.356</v>
       </c>
       <c r="G24">
         <v>0.192</v>
@@ -3255,37 +3255,37 @@
         <v>1.815</v>
       </c>
       <c r="M24">
-        <v>5.0423472</v>
+        <v>5.271544800000001</v>
       </c>
       <c r="N24">
-        <v>-3.227347200000001</v>
+        <v>-3.456544800000001</v>
       </c>
       <c r="O24">
-        <v>-1.032751104</v>
+        <v>-1.106094336</v>
       </c>
       <c r="P24">
-        <v>-2.194596096000001</v>
+        <v>-2.350450464000001</v>
       </c>
       <c r="Q24">
-        <v>1.265403903999999</v>
+        <v>1.109549535999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09390006542593476</v>
+        <v>0.09452474160029754</v>
       </c>
       <c r="T24">
-        <v>0.6269050984195791</v>
+        <v>0.6350467230743788</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.1151844521932166</v>
+        <v>0.110176432532642</v>
       </c>
       <c r="W24">
-        <v>0.2086395061728395</v>
+        <v>0.209820397208803</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3599514131038021</v>
+        <v>0.3443013516645063</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1210427423902538</v>
+        <v>0.1229427423902538</v>
       </c>
       <c r="C25">
-        <v>27.01863228758236</v>
+        <v>24.83528046820224</v>
       </c>
       <c r="D25">
-        <v>49.18263228758236</v>
+        <v>47.97128046820225</v>
       </c>
       <c r="E25">
-        <v>5.156000000000002</v>
+        <v>6.128000000000004</v>
       </c>
       <c r="F25">
-        <v>22.356</v>
+        <v>23.328</v>
       </c>
       <c r="G25">
         <v>0.192</v>
@@ -3337,37 +3337,37 @@
         <v>1.815</v>
       </c>
       <c r="M25">
-        <v>5.271544800000001</v>
+        <v>5.500742400000001</v>
       </c>
       <c r="N25">
-        <v>-3.456544800000001</v>
+        <v>-3.685742400000001</v>
       </c>
       <c r="O25">
-        <v>-1.106094336</v>
+        <v>-1.179437568</v>
       </c>
       <c r="P25">
-        <v>-2.350450464000001</v>
+        <v>-2.506304832000001</v>
       </c>
       <c r="Q25">
-        <v>1.109549535999999</v>
+        <v>0.953695167999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09452474160029754</v>
+        <v>0.0951658566213541</v>
       </c>
       <c r="T25">
-        <v>0.6350467230743788</v>
+        <v>0.643402601009568</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.110176432532642</v>
+        <v>0.1055857478437819</v>
       </c>
       <c r="W25">
-        <v>0.209820397208803</v>
+        <v>0.2109028806584362</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3443013516645063</v>
+        <v>0.3299554620118185</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1229427423902538</v>
+        <v>0.1248427423902538</v>
       </c>
       <c r="C26">
-        <v>24.83528046820225</v>
+        <v>22.71016469649007</v>
       </c>
       <c r="D26">
-        <v>47.97128046820225</v>
+        <v>46.81816469649007</v>
       </c>
       <c r="E26">
-        <v>6.128</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="F26">
-        <v>23.328</v>
+        <v>24.3</v>
       </c>
       <c r="G26">
         <v>0.192</v>
@@ -3419,37 +3419,37 @@
         <v>1.815</v>
       </c>
       <c r="M26">
-        <v>5.5007424</v>
+        <v>5.72994</v>
       </c>
       <c r="N26">
-        <v>-3.685742400000001</v>
+        <v>-3.914940000000001</v>
       </c>
       <c r="O26">
-        <v>-1.179437568</v>
+        <v>-1.2527808</v>
       </c>
       <c r="P26">
-        <v>-2.506304832000001</v>
+        <v>-2.662159200000001</v>
       </c>
       <c r="Q26">
-        <v>0.9536951679999994</v>
+        <v>0.7978407999999995</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0951658566213541</v>
+        <v>0.09582406804297214</v>
       </c>
       <c r="T26">
-        <v>0.643402601009568</v>
+        <v>0.6519813023563622</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.1055857478437819</v>
+        <v>0.1013623179300306</v>
       </c>
       <c r="W26">
-        <v>0.2109028806584362</v>
+        <v>0.2118987654320988</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3299554620118186</v>
+        <v>0.3167572435313458</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1248427423902538</v>
+        <v>0.1267427423902538</v>
       </c>
       <c r="C27">
-        <v>22.71016469649007</v>
+        <v>20.63918398127719</v>
       </c>
       <c r="D27">
-        <v>46.81816469649007</v>
+        <v>45.71918398127719</v>
       </c>
       <c r="E27">
-        <v>7.100000000000001</v>
+        <v>8.072000000000003</v>
       </c>
       <c r="F27">
-        <v>24.3</v>
+        <v>25.272</v>
       </c>
       <c r="G27">
         <v>0.192</v>
@@ -3501,37 +3501,37 @@
         <v>1.815</v>
       </c>
       <c r="M27">
-        <v>5.72994</v>
+        <v>5.959137600000001</v>
       </c>
       <c r="N27">
-        <v>-3.914940000000001</v>
+        <v>-4.144137600000001</v>
       </c>
       <c r="O27">
-        <v>-1.2527808</v>
+        <v>-1.326124032000001</v>
       </c>
       <c r="P27">
-        <v>-2.662159200000001</v>
+        <v>-2.818013568000001</v>
       </c>
       <c r="Q27">
-        <v>0.7978407999999995</v>
+        <v>0.6419864319999991</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09582406804297214</v>
+        <v>0.09650006896247176</v>
       </c>
       <c r="T27">
-        <v>0.6519813023563622</v>
+        <v>0.6607918604963131</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1013623179300306</v>
+        <v>0.09746376724041408</v>
       </c>
       <c r="W27">
-        <v>0.2118987654320988</v>
+        <v>0.2128180436847104</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3167572435313458</v>
+        <v>0.304574272626294</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1267427423902538</v>
+        <v>0.1286427423902538</v>
       </c>
       <c r="C28">
-        <v>20.63918398127719</v>
+        <v>18.61861355666211</v>
       </c>
       <c r="D28">
-        <v>45.71918398127719</v>
+        <v>44.67061355666211</v>
       </c>
       <c r="E28">
-        <v>8.072000000000003</v>
+        <v>9.044000000000004</v>
       </c>
       <c r="F28">
-        <v>25.272</v>
+        <v>26.244</v>
       </c>
       <c r="G28">
         <v>0.192</v>
@@ -3583,37 +3583,37 @@
         <v>1.815</v>
       </c>
       <c r="M28">
-        <v>5.959137600000001</v>
+        <v>6.188335200000001</v>
       </c>
       <c r="N28">
-        <v>-4.144137600000001</v>
+        <v>-4.373335200000001</v>
       </c>
       <c r="O28">
-        <v>-1.326124032000001</v>
+        <v>-1.399467264000001</v>
       </c>
       <c r="P28">
-        <v>-2.818013568000001</v>
+        <v>-2.973867936000001</v>
       </c>
       <c r="Q28">
-        <v>0.6419864319999991</v>
+        <v>0.4861320639999991</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09650006896247176</v>
+        <v>0.09719459045510837</v>
       </c>
       <c r="T28">
-        <v>0.6607918604963131</v>
+        <v>0.6698438037907831</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.09746376724041408</v>
+        <v>0.09385399808336171</v>
       </c>
       <c r="W28">
-        <v>0.2128180436847104</v>
+        <v>0.2136692272519433</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.304574272626294</v>
+        <v>0.2932937440105053</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1286427423902538</v>
+        <v>0.1305427423902538</v>
       </c>
       <c r="C29">
-        <v>18.61861355666211</v>
+        <v>16.64506270565472</v>
       </c>
       <c r="D29">
-        <v>44.67061355666211</v>
+        <v>43.66906270565472</v>
       </c>
       <c r="E29">
-        <v>9.044000000000004</v>
+        <v>10.01600000000001</v>
       </c>
       <c r="F29">
-        <v>26.244</v>
+        <v>27.216</v>
       </c>
       <c r="G29">
         <v>0.192</v>
@@ -3665,37 +3665,37 @@
         <v>1.815</v>
       </c>
       <c r="M29">
-        <v>6.188335200000001</v>
+        <v>6.417532800000001</v>
       </c>
       <c r="N29">
-        <v>-4.373335200000001</v>
+        <v>-4.602532800000001</v>
       </c>
       <c r="O29">
-        <v>-1.399467264000001</v>
+        <v>-1.472810496000001</v>
       </c>
       <c r="P29">
-        <v>-2.973867936000001</v>
+        <v>-3.129722304000001</v>
       </c>
       <c r="Q29">
-        <v>0.4861320639999991</v>
+        <v>0.3302776959999991</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09719459045510837</v>
+        <v>0.09790840421142932</v>
       </c>
       <c r="T29">
-        <v>0.6698438037907831</v>
+        <v>0.679147189954544</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09385399808336171</v>
+        <v>0.09050206958038449</v>
       </c>
       <c r="W29">
-        <v>0.2136692272519433</v>
+        <v>0.2144596119929453</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2932937440105053</v>
+        <v>0.2828189674387016</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1305427423902538</v>
+        <v>0.1324427423902538</v>
       </c>
       <c r="C30">
-        <v>16.64506270565472</v>
+        <v>14.7154381331657</v>
       </c>
       <c r="D30">
-        <v>43.66906270565472</v>
+        <v>42.71143813316571</v>
       </c>
       <c r="E30">
-        <v>10.01600000000001</v>
+        <v>10.98800000000001</v>
       </c>
       <c r="F30">
-        <v>27.216</v>
+        <v>28.18800000000001</v>
       </c>
       <c r="G30">
         <v>0.192</v>
@@ -3747,37 +3747,37 @@
         <v>1.815</v>
       </c>
       <c r="M30">
-        <v>6.417532800000001</v>
+        <v>6.646730400000002</v>
       </c>
       <c r="N30">
-        <v>-4.602532800000001</v>
+        <v>-4.831730400000002</v>
       </c>
       <c r="O30">
-        <v>-1.472810496000001</v>
+        <v>-1.546153728000001</v>
       </c>
       <c r="P30">
-        <v>-3.129722304000001</v>
+        <v>-3.285576672000001</v>
       </c>
       <c r="Q30">
-        <v>0.3302776959999991</v>
+        <v>0.1744233279999987</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09790840421142932</v>
+        <v>0.09864232539750578</v>
       </c>
       <c r="T30">
-        <v>0.679147189954544</v>
+        <v>0.6887126433341855</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09050206958038449</v>
+        <v>0.08738130856037123</v>
       </c>
       <c r="W30">
-        <v>0.2144596119929453</v>
+        <v>0.2151954874414645</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2828189674387016</v>
+        <v>0.2730665892511601</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1324427423902538</v>
+        <v>0.1343427423902538</v>
       </c>
       <c r="C31">
-        <v>14.71543813316572</v>
+        <v>12.82691205477368</v>
       </c>
       <c r="D31">
-        <v>42.71143813316571</v>
+        <v>41.79491205477368</v>
       </c>
       <c r="E31">
-        <v>10.988</v>
+        <v>11.96</v>
       </c>
       <c r="F31">
-        <v>28.188</v>
+        <v>29.16</v>
       </c>
       <c r="G31">
         <v>0.192</v>
@@ -3829,37 +3829,37 @@
         <v>1.815</v>
       </c>
       <c r="M31">
-        <v>6.6467304</v>
+        <v>6.875928</v>
       </c>
       <c r="N31">
-        <v>-4.831730400000001</v>
+        <v>-5.060928000000001</v>
       </c>
       <c r="O31">
-        <v>-1.546153728</v>
+        <v>-1.61949696</v>
       </c>
       <c r="P31">
-        <v>-3.285576672</v>
+        <v>-3.44143104</v>
       </c>
       <c r="Q31">
-        <v>0.1744233279999996</v>
+        <v>0.01856895999999963</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09864232539750578</v>
+        <v>0.09939721576032731</v>
       </c>
       <c r="T31">
-        <v>0.6887126433341855</v>
+        <v>0.6985513953818168</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08738130856037125</v>
+        <v>0.08446859827502555</v>
       </c>
       <c r="W31">
-        <v>0.2151954874414645</v>
+        <v>0.215882304526749</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2730665892511601</v>
+        <v>0.2639643696094548</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1343427423902538</v>
+        <v>0.1362427423902538</v>
       </c>
       <c r="C32">
-        <v>12.82691205477368</v>
+        <v>10.97689430779493</v>
       </c>
       <c r="D32">
-        <v>41.79491205477368</v>
+        <v>40.91689430779493</v>
       </c>
       <c r="E32">
-        <v>11.96</v>
+        <v>12.932</v>
       </c>
       <c r="F32">
-        <v>29.16</v>
+        <v>30.132</v>
       </c>
       <c r="G32">
         <v>0.192</v>
@@ -3911,37 +3911,37 @@
         <v>1.815</v>
       </c>
       <c r="M32">
-        <v>6.875928</v>
+        <v>7.105125600000001</v>
       </c>
       <c r="N32">
-        <v>-5.060928000000001</v>
+        <v>-5.290125600000001</v>
       </c>
       <c r="O32">
-        <v>-1.61949696</v>
+        <v>-1.692840192</v>
       </c>
       <c r="P32">
-        <v>-3.44143104</v>
+        <v>-3.597285408000001</v>
       </c>
       <c r="Q32">
-        <v>0.01856895999999963</v>
+        <v>-0.1372854080000012</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09939721576032731</v>
+        <v>0.1001739870032306</v>
       </c>
       <c r="T32">
-        <v>0.6985513953818168</v>
+        <v>0.7086753286482199</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08446859827502555</v>
+        <v>0.08174380478228278</v>
       </c>
       <c r="W32">
-        <v>0.215882304526749</v>
+        <v>0.2165248108323377</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2639643696094548</v>
+        <v>0.2554493899446336</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1362427423902538</v>
+        <v>0.1381427423902538</v>
       </c>
       <c r="C33">
-        <v>10.97689430779493</v>
+        <v>9.163007905328545</v>
       </c>
       <c r="D33">
-        <v>40.91689430779493</v>
+        <v>40.07500790532855</v>
       </c>
       <c r="E33">
-        <v>12.932</v>
+        <v>13.904</v>
       </c>
       <c r="F33">
-        <v>30.132</v>
+        <v>31.104</v>
       </c>
       <c r="G33">
         <v>0.192</v>
@@ -3993,37 +3993,37 @@
         <v>1.815</v>
       </c>
       <c r="M33">
-        <v>7.105125600000001</v>
+        <v>7.334323200000001</v>
       </c>
       <c r="N33">
-        <v>-5.290125600000001</v>
+        <v>-5.519323200000001</v>
       </c>
       <c r="O33">
-        <v>-1.692840192</v>
+        <v>-1.766183424000001</v>
       </c>
       <c r="P33">
-        <v>-3.597285408000001</v>
+        <v>-3.753139776000001</v>
       </c>
       <c r="Q33">
-        <v>-0.1372854080000012</v>
+        <v>-0.2931397760000012</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1001739870032306</v>
+        <v>0.1009736044591605</v>
       </c>
       <c r="T33">
-        <v>0.7086753286482199</v>
+        <v>0.7190970246577525</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08174380478228278</v>
+        <v>0.07918931088283644</v>
       </c>
       <c r="W33">
-        <v>0.2165248108323377</v>
+        <v>0.2171271604938272</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2554493899446336</v>
+        <v>0.2474665965088638</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1381427423902538</v>
+        <v>0.1400427423902538</v>
       </c>
       <c r="C34">
-        <v>9.163007905328545</v>
+        <v>7.383067547387533</v>
       </c>
       <c r="D34">
-        <v>40.07500790532855</v>
+        <v>39.26706754738753</v>
       </c>
       <c r="E34">
-        <v>13.904</v>
+        <v>14.876</v>
       </c>
       <c r="F34">
-        <v>31.104</v>
+        <v>32.076</v>
       </c>
       <c r="G34">
         <v>0.192</v>
@@ -4075,37 +4075,37 @@
         <v>1.815</v>
       </c>
       <c r="M34">
-        <v>7.334323200000001</v>
+        <v>7.5635208</v>
       </c>
       <c r="N34">
-        <v>-5.519323200000001</v>
+        <v>-5.748520800000001</v>
       </c>
       <c r="O34">
-        <v>-1.766183424000001</v>
+        <v>-1.839526656</v>
       </c>
       <c r="P34">
-        <v>-3.753139776000001</v>
+        <v>-3.908994144</v>
       </c>
       <c r="Q34">
-        <v>-0.2931397760000012</v>
+        <v>-0.4489941440000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1009736044591605</v>
+        <v>0.1017970910928793</v>
       </c>
       <c r="T34">
-        <v>0.7190970246577525</v>
+        <v>0.7298298160705549</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07918931088283644</v>
+        <v>0.07678963479547778</v>
       </c>
       <c r="W34">
-        <v>0.2171271604938272</v>
+        <v>0.2176930041152264</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2474665965088638</v>
+        <v>0.239967608735868</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1400427423902538</v>
+        <v>0.1419427423902538</v>
       </c>
       <c r="C35">
-        <v>7.383067547387533</v>
+        <v>5.635060680044418</v>
       </c>
       <c r="D35">
-        <v>39.26706754738753</v>
+        <v>38.49106068004442</v>
       </c>
       <c r="E35">
-        <v>14.876</v>
+        <v>15.848</v>
       </c>
       <c r="F35">
-        <v>32.076</v>
+        <v>33.048</v>
       </c>
       <c r="G35">
         <v>0.192</v>
@@ -4157,37 +4157,37 @@
         <v>1.815</v>
       </c>
       <c r="M35">
-        <v>7.5635208</v>
+        <v>7.792718400000001</v>
       </c>
       <c r="N35">
-        <v>-5.748520800000001</v>
+        <v>-5.977718400000001</v>
       </c>
       <c r="O35">
-        <v>-1.839526656</v>
+        <v>-1.912869888000001</v>
       </c>
       <c r="P35">
-        <v>-3.908994144</v>
+        <v>-4.064848512000001</v>
       </c>
       <c r="Q35">
-        <v>-0.4489941440000003</v>
+        <v>-0.6048485120000011</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1017970910928793</v>
+        <v>0.1026455318670138</v>
       </c>
       <c r="T35">
-        <v>0.7298298160705549</v>
+        <v>0.7408878435867754</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07678963479547778</v>
+        <v>0.07453111612502253</v>
       </c>
       <c r="W35">
-        <v>0.2176930041152264</v>
+        <v>0.2182255628177197</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.239967608735868</v>
+        <v>0.2329097378906954</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1419427423902538</v>
+        <v>0.1438427423902538</v>
       </c>
       <c r="C36">
-        <v>5.635060680044418</v>
+        <v>3.917130756940239</v>
       </c>
       <c r="D36">
-        <v>38.49106068004442</v>
+        <v>37.74513075694024</v>
       </c>
       <c r="E36">
-        <v>15.848</v>
+        <v>16.82</v>
       </c>
       <c r="F36">
-        <v>33.048</v>
+        <v>34.02</v>
       </c>
       <c r="G36">
         <v>0.192</v>
@@ -4239,37 +4239,37 @@
         <v>1.815</v>
       </c>
       <c r="M36">
-        <v>7.792718400000001</v>
+        <v>8.021916000000001</v>
       </c>
       <c r="N36">
-        <v>-5.977718400000001</v>
+        <v>-6.206916000000001</v>
       </c>
       <c r="O36">
-        <v>-1.912869888000001</v>
+        <v>-1.986213120000001</v>
       </c>
       <c r="P36">
-        <v>-4.064848512000001</v>
+        <v>-4.220702880000001</v>
       </c>
       <c r="Q36">
-        <v>-0.6048485120000011</v>
+        <v>-0.7607028800000011</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1026455318670138</v>
+        <v>0.1035200785111217</v>
       </c>
       <c r="T36">
-        <v>0.7408878435867754</v>
+        <v>0.752286118103495</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07453111612502253</v>
+        <v>0.0724016556643076</v>
       </c>
       <c r="W36">
-        <v>0.2182255628177197</v>
+        <v>0.2187276895943563</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2329097378906954</v>
+        <v>0.2262551739509613</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1438427423902538</v>
+        <v>0.1457427423902538</v>
       </c>
       <c r="C37">
-        <v>3.917130756940239</v>
+        <v>2.227562410074675</v>
       </c>
       <c r="D37">
-        <v>37.74513075694024</v>
+        <v>37.02756241007468</v>
       </c>
       <c r="E37">
-        <v>16.82</v>
+        <v>17.79200000000001</v>
       </c>
       <c r="F37">
-        <v>34.02</v>
+        <v>34.992</v>
       </c>
       <c r="G37">
         <v>0.192</v>
@@ -4321,37 +4321,37 @@
         <v>1.815</v>
       </c>
       <c r="M37">
-        <v>8.021916000000001</v>
+        <v>8.251113600000002</v>
       </c>
       <c r="N37">
-        <v>-6.206916000000001</v>
+        <v>-6.436113600000002</v>
       </c>
       <c r="O37">
-        <v>-1.986213120000001</v>
+        <v>-2.059556352000001</v>
       </c>
       <c r="P37">
-        <v>-4.220702880000001</v>
+        <v>-4.376557248000001</v>
       </c>
       <c r="Q37">
-        <v>-0.7607028800000011</v>
+        <v>-0.916557248000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1035200785111217</v>
+        <v>0.104421954737858</v>
       </c>
       <c r="T37">
-        <v>0.752286118103495</v>
+        <v>0.764040588698862</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0724016556643076</v>
+        <v>0.07039049856252128</v>
       </c>
       <c r="W37">
-        <v>0.2187276895943563</v>
+        <v>0.2192019204389575</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2262551739509613</v>
+        <v>0.219970308007879</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1457427423902538</v>
+        <v>0.1476427423902538</v>
       </c>
       <c r="C38">
-        <v>2.227562410074682</v>
+        <v>0.5647682805376206</v>
       </c>
       <c r="D38">
-        <v>37.02756241007468</v>
+        <v>36.33676828053762</v>
       </c>
       <c r="E38">
-        <v>17.792</v>
+        <v>18.764</v>
       </c>
       <c r="F38">
-        <v>34.992</v>
+        <v>35.964</v>
       </c>
       <c r="G38">
         <v>0.192</v>
@@ -4403,37 +4403,37 @@
         <v>1.815</v>
       </c>
       <c r="M38">
-        <v>8.2511136</v>
+        <v>8.480311199999999</v>
       </c>
       <c r="N38">
-        <v>-6.436113600000001</v>
+        <v>-6.6653112</v>
       </c>
       <c r="O38">
-        <v>-2.059556352</v>
+        <v>-2.132899584</v>
       </c>
       <c r="P38">
-        <v>-4.376557248</v>
+        <v>-4.532411615999999</v>
       </c>
       <c r="Q38">
-        <v>-0.9165572480000002</v>
+        <v>-1.072411615999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.104421954737858</v>
+        <v>0.1053524619559192</v>
       </c>
       <c r="T38">
-        <v>0.764040588698862</v>
+        <v>0.7761682170909076</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07039049856252129</v>
+        <v>0.06848805265542612</v>
       </c>
       <c r="W38">
-        <v>0.2192019204389575</v>
+        <v>0.2196505171838505</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.219970308007879</v>
+        <v>0.2140251645482066</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1476427423902538</v>
+        <v>0.1495427423902538</v>
       </c>
       <c r="C39">
-        <v>0.5647682805376206</v>
+        <v>-1.072722703625018</v>
       </c>
       <c r="D39">
-        <v>36.33676828053762</v>
+        <v>35.67127729637498</v>
       </c>
       <c r="E39">
-        <v>18.764</v>
+        <v>19.736</v>
       </c>
       <c r="F39">
-        <v>35.964</v>
+        <v>36.936</v>
       </c>
       <c r="G39">
         <v>0.192</v>
@@ -4485,37 +4485,37 @@
         <v>1.815</v>
       </c>
       <c r="M39">
-        <v>8.480311199999999</v>
+        <v>8.7095088</v>
       </c>
       <c r="N39">
-        <v>-6.6653112</v>
+        <v>-6.894508800000001</v>
       </c>
       <c r="O39">
-        <v>-2.132899584</v>
+        <v>-2.206242816</v>
       </c>
       <c r="P39">
-        <v>-4.532411615999999</v>
+        <v>-4.688265984000001</v>
       </c>
       <c r="Q39">
-        <v>-1.072411615999999</v>
+        <v>-1.228265984000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1053524619559192</v>
+        <v>0.1063129855358534</v>
       </c>
       <c r="T39">
-        <v>0.7761682170909076</v>
+        <v>0.7886870593020511</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06848805265542612</v>
+        <v>0.06668573548028332</v>
       </c>
       <c r="W39">
-        <v>0.2196505171838505</v>
+        <v>0.2200755035737492</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2140251645482066</v>
+        <v>0.2083929233758854</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1495427423902538</v>
+        <v>0.1514427423902538</v>
       </c>
       <c r="C40">
-        <v>-1.072722703625018</v>
+        <v>-2.686275784599992</v>
       </c>
       <c r="D40">
-        <v>35.67127729637498</v>
+        <v>35.02972421540001</v>
       </c>
       <c r="E40">
-        <v>19.736</v>
+        <v>20.708</v>
       </c>
       <c r="F40">
-        <v>36.936</v>
+        <v>37.908</v>
       </c>
       <c r="G40">
         <v>0.192</v>
@@ -4567,37 +4567,37 @@
         <v>1.815</v>
       </c>
       <c r="M40">
-        <v>8.7095088</v>
+        <v>8.938706400000001</v>
       </c>
       <c r="N40">
-        <v>-6.894508800000001</v>
+        <v>-7.123706400000001</v>
       </c>
       <c r="O40">
-        <v>-2.206242816</v>
+        <v>-2.279586048000001</v>
       </c>
       <c r="P40">
-        <v>-4.688265984000001</v>
+        <v>-4.844120352000001</v>
       </c>
       <c r="Q40">
-        <v>-1.228265984000001</v>
+        <v>-1.384120352000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1063129855358534</v>
+        <v>0.1073050016921789</v>
       </c>
       <c r="T40">
-        <v>0.7886870593020511</v>
+        <v>0.8016163553561831</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06668573548028332</v>
+        <v>0.06497584482694271</v>
       </c>
       <c r="W40">
-        <v>0.2200755035737492</v>
+        <v>0.2204786957898069</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2083929233758854</v>
+        <v>0.203049515084196</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1514427423902538</v>
+        <v>0.1533427423902538</v>
       </c>
       <c r="C41">
-        <v>-2.686275784599992</v>
+        <v>-4.277159723487635</v>
       </c>
       <c r="D41">
-        <v>35.02972421540001</v>
+        <v>34.41084027651237</v>
       </c>
       <c r="E41">
-        <v>20.708</v>
+        <v>21.68</v>
       </c>
       <c r="F41">
-        <v>37.908</v>
+        <v>38.88</v>
       </c>
       <c r="G41">
         <v>0.192</v>
@@ -4649,37 +4649,37 @@
         <v>1.815</v>
       </c>
       <c r="M41">
-        <v>8.938706400000001</v>
+        <v>9.167904000000002</v>
       </c>
       <c r="N41">
-        <v>-7.123706400000001</v>
+        <v>-7.352904000000002</v>
       </c>
       <c r="O41">
-        <v>-2.279586048000001</v>
+        <v>-2.352929280000001</v>
       </c>
       <c r="P41">
-        <v>-4.844120352000001</v>
+        <v>-4.999974720000001</v>
       </c>
       <c r="Q41">
-        <v>-1.384120352000001</v>
+        <v>-1.539974720000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1073050016921789</v>
+        <v>0.1083300850537152</v>
       </c>
       <c r="T41">
-        <v>0.8016163553561831</v>
+        <v>0.8149766279454528</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06497584482694271</v>
+        <v>0.06335144870626915</v>
       </c>
       <c r="W41">
-        <v>0.2204786957898069</v>
+        <v>0.2208617283950617</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.203049515084196</v>
+        <v>0.1979732772070911</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1533427423902538</v>
+        <v>0.1552427423902538</v>
       </c>
       <c r="C42">
-        <v>-4.277159723487635</v>
+        <v>-5.846555175186374</v>
       </c>
       <c r="D42">
-        <v>34.41084027651237</v>
+        <v>33.81344482481363</v>
       </c>
       <c r="E42">
-        <v>21.68</v>
+        <v>22.652</v>
       </c>
       <c r="F42">
-        <v>38.88</v>
+        <v>39.852</v>
       </c>
       <c r="G42">
         <v>0.192</v>
@@ -4731,37 +4731,37 @@
         <v>1.815</v>
       </c>
       <c r="M42">
-        <v>9.167904000000002</v>
+        <v>9.397101600000001</v>
       </c>
       <c r="N42">
-        <v>-7.352904000000002</v>
+        <v>-7.582101600000001</v>
       </c>
       <c r="O42">
-        <v>-2.352929280000001</v>
+        <v>-2.426272512000001</v>
       </c>
       <c r="P42">
-        <v>-4.999974720000001</v>
+        <v>-5.155829088000001</v>
       </c>
       <c r="Q42">
-        <v>-1.539974720000001</v>
+        <v>-1.695829088000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1083300850537152</v>
+        <v>0.1093899170037781</v>
       </c>
       <c r="T42">
-        <v>0.8149766279454528</v>
+        <v>0.828789791130969</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06335144870626915</v>
+        <v>0.0618062914207504</v>
       </c>
       <c r="W42">
-        <v>0.2208617283950617</v>
+        <v>0.2212260764829871</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1979732772070911</v>
+        <v>0.1931446606898449</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1552427423902538</v>
+        <v>0.1571427423902538</v>
       </c>
       <c r="C43">
-        <v>-5.846555175186374</v>
+        <v>-7.395562205801511</v>
       </c>
       <c r="D43">
-        <v>33.81344482481363</v>
+        <v>33.23643779419849</v>
       </c>
       <c r="E43">
-        <v>22.652</v>
+        <v>23.62400000000001</v>
       </c>
       <c r="F43">
-        <v>39.852</v>
+        <v>40.82400000000001</v>
       </c>
       <c r="G43">
         <v>0.192</v>
@@ -4813,37 +4813,37 @@
         <v>1.815</v>
       </c>
       <c r="M43">
-        <v>9.397101600000001</v>
+        <v>9.626299200000002</v>
       </c>
       <c r="N43">
-        <v>-7.582101600000001</v>
+        <v>-7.811299200000002</v>
       </c>
       <c r="O43">
-        <v>-2.426272512000001</v>
+        <v>-2.499615744000001</v>
       </c>
       <c r="P43">
-        <v>-5.155829088000001</v>
+        <v>-5.311683456000002</v>
       </c>
       <c r="Q43">
-        <v>-1.695829088000001</v>
+        <v>-1.851683456000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1093899170037781</v>
+        <v>0.1104862948831536</v>
       </c>
       <c r="T43">
-        <v>0.828789791130969</v>
+        <v>0.8430792702883995</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0618062914207504</v>
+        <v>0.06033471305358967</v>
       </c>
       <c r="W43">
-        <v>0.2212260764829871</v>
+        <v>0.2215730746619636</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1931446606898449</v>
+        <v>0.1885459782924677</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1571427423902538</v>
+        <v>0.1590427423902538</v>
       </c>
       <c r="C44">
-        <v>-7.395562205801504</v>
+        <v>-8.92520705328635</v>
       </c>
       <c r="D44">
-        <v>33.23643779419849</v>
+        <v>32.67879294671365</v>
       </c>
       <c r="E44">
-        <v>23.624</v>
+        <v>24.596</v>
       </c>
       <c r="F44">
-        <v>40.824</v>
+        <v>41.796</v>
       </c>
       <c r="G44">
         <v>0.192</v>
@@ -4895,37 +4895,37 @@
         <v>1.815</v>
       </c>
       <c r="M44">
-        <v>9.6262992</v>
+        <v>9.855496800000001</v>
       </c>
       <c r="N44">
-        <v>-7.811299200000001</v>
+        <v>-8.040496800000001</v>
       </c>
       <c r="O44">
-        <v>-2.499615744</v>
+        <v>-2.572958976000001</v>
       </c>
       <c r="P44">
-        <v>-5.311683456000001</v>
+        <v>-5.467537824000001</v>
       </c>
       <c r="Q44">
-        <v>-1.851683456000001</v>
+        <v>-2.007537824000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1104862948831536</v>
+        <v>0.1116211421618055</v>
       </c>
       <c r="T44">
-        <v>0.8430792702883994</v>
+        <v>0.857870134679424</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06033471305358967</v>
+        <v>0.05893158019187828</v>
       </c>
       <c r="W44">
-        <v>0.2215730746619636</v>
+        <v>0.2219039333907551</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1885459782924678</v>
+        <v>0.1841611880996197</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1590427423902538</v>
+        <v>0.1609427423902538</v>
       </c>
       <c r="C45">
-        <v>-8.92520705328635</v>
+        <v>-10.43644821872876</v>
       </c>
       <c r="D45">
-        <v>32.67879294671365</v>
+        <v>32.13955178127124</v>
       </c>
       <c r="E45">
-        <v>24.596</v>
+        <v>25.568</v>
       </c>
       <c r="F45">
-        <v>41.796</v>
+        <v>42.768</v>
       </c>
       <c r="G45">
         <v>0.192</v>
@@ -4977,37 +4977,37 @@
         <v>1.815</v>
       </c>
       <c r="M45">
-        <v>9.855496800000001</v>
+        <v>10.0846944</v>
       </c>
       <c r="N45">
-        <v>-8.040496800000001</v>
+        <v>-8.269694400000001</v>
       </c>
       <c r="O45">
-        <v>-2.572958976000001</v>
+        <v>-2.646302208</v>
       </c>
       <c r="P45">
-        <v>-5.467537824000001</v>
+        <v>-5.623392192000001</v>
       </c>
       <c r="Q45">
-        <v>-2.007537824000001</v>
+        <v>-2.163392192000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1116211421618055</v>
+        <v>0.1127965197004091</v>
       </c>
       <c r="T45">
-        <v>0.857870134679424</v>
+        <v>0.873189244227271</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05893158019187828</v>
+        <v>0.05759222609660832</v>
       </c>
       <c r="W45">
-        <v>0.2219039333907551</v>
+        <v>0.2222197530864198</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1841611880996197</v>
+        <v>0.179975706551901</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1609427423902538</v>
+        <v>0.1628427423902538</v>
       </c>
       <c r="C46">
-        <v>-10.43644821872876</v>
+        <v>-11.93018196434458</v>
       </c>
       <c r="D46">
-        <v>32.13955178127124</v>
+        <v>31.61781803565543</v>
       </c>
       <c r="E46">
-        <v>25.568</v>
+        <v>26.54</v>
       </c>
       <c r="F46">
-        <v>42.768</v>
+        <v>43.74</v>
       </c>
       <c r="G46">
         <v>0.192</v>
@@ -5059,37 +5059,37 @@
         <v>1.815</v>
       </c>
       <c r="M46">
-        <v>10.0846944</v>
+        <v>10.313892</v>
       </c>
       <c r="N46">
-        <v>-8.269694400000001</v>
+        <v>-8.498892000000001</v>
       </c>
       <c r="O46">
-        <v>-2.646302208</v>
+        <v>-2.71964544</v>
       </c>
       <c r="P46">
-        <v>-5.623392192000001</v>
+        <v>-5.779246560000001</v>
       </c>
       <c r="Q46">
-        <v>-2.163392192000001</v>
+        <v>-2.319246560000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1127965197004091</v>
+        <v>0.1140146382404165</v>
       </c>
       <c r="T46">
-        <v>0.873189244227271</v>
+        <v>0.8890654123041303</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05759222609660832</v>
+        <v>0.05631239885001702</v>
       </c>
       <c r="W46">
-        <v>0.2222197530864198</v>
+        <v>0.222521536351166</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.179975706551901</v>
+        <v>0.1759762464063032</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1628427423902538</v>
+        <v>0.1647427423902538</v>
       </c>
       <c r="C47">
-        <v>-11.93018196434458</v>
+        <v>-13.4072472845189</v>
       </c>
       <c r="D47">
-        <v>31.61781803565543</v>
+        <v>31.1127527154811</v>
       </c>
       <c r="E47">
-        <v>26.54</v>
+        <v>27.512</v>
       </c>
       <c r="F47">
-        <v>43.74</v>
+        <v>44.712</v>
       </c>
       <c r="G47">
         <v>0.192</v>
@@ -5141,37 +5141,37 @@
         <v>1.815</v>
       </c>
       <c r="M47">
-        <v>10.313892</v>
+        <v>10.5430896</v>
       </c>
       <c r="N47">
-        <v>-8.498892000000001</v>
+        <v>-8.728089600000002</v>
       </c>
       <c r="O47">
-        <v>-2.71964544</v>
+        <v>-2.792988672000001</v>
       </c>
       <c r="P47">
-        <v>-5.779246560000001</v>
+        <v>-5.935100928000002</v>
       </c>
       <c r="Q47">
-        <v>-2.319246560000001</v>
+        <v>-2.475100928000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1140146382404165</v>
+        <v>0.1152778722819058</v>
       </c>
       <c r="T47">
-        <v>0.8890654123041303</v>
+        <v>0.9055295866060588</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05631239885001702</v>
+        <v>0.055088216266321</v>
       </c>
       <c r="W47">
-        <v>0.222521536351166</v>
+        <v>0.2228101986044015</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1759762464063032</v>
+        <v>0.1721506758322531</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1647427423902538</v>
+        <v>0.1666427423902538</v>
       </c>
       <c r="C48">
-        <v>-13.4072472845189</v>
+        <v>-14.86843040789183</v>
       </c>
       <c r="D48">
-        <v>31.1127527154811</v>
+        <v>30.62356959210818</v>
       </c>
       <c r="E48">
-        <v>27.512</v>
+        <v>28.48400000000001</v>
       </c>
       <c r="F48">
-        <v>44.712</v>
+        <v>45.684</v>
       </c>
       <c r="G48">
         <v>0.192</v>
@@ -5223,37 +5223,37 @@
         <v>1.815</v>
       </c>
       <c r="M48">
-        <v>10.5430896</v>
+        <v>10.7722872</v>
       </c>
       <c r="N48">
-        <v>-8.728089600000002</v>
+        <v>-8.957287200000001</v>
       </c>
       <c r="O48">
-        <v>-2.792988672000001</v>
+        <v>-2.866331904</v>
       </c>
       <c r="P48">
-        <v>-5.935100928000002</v>
+        <v>-6.090955296000001</v>
       </c>
       <c r="Q48">
-        <v>-2.475100928000002</v>
+        <v>-2.630955296000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1152778722819058</v>
+        <v>0.1165887755325077</v>
       </c>
       <c r="T48">
-        <v>0.9055295866060588</v>
+        <v>0.9226150505042862</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.055088216266321</v>
+        <v>0.05391612655852694</v>
       </c>
       <c r="W48">
-        <v>0.2228101986044015</v>
+        <v>0.2230865773574993</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1721506758322531</v>
+        <v>0.1684878954953967</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1666427423902538</v>
+        <v>0.1685427423902538</v>
       </c>
       <c r="C49">
-        <v>-14.86843040789183</v>
+        <v>-16.31446888130323</v>
       </c>
       <c r="D49">
-        <v>30.62356959210818</v>
+        <v>30.14953111869677</v>
       </c>
       <c r="E49">
-        <v>28.48400000000001</v>
+        <v>29.45600000000001</v>
       </c>
       <c r="F49">
-        <v>45.684</v>
+        <v>46.65600000000001</v>
       </c>
       <c r="G49">
         <v>0.192</v>
@@ -5305,37 +5305,37 @@
         <v>1.815</v>
       </c>
       <c r="M49">
-        <v>10.7722872</v>
+        <v>11.0014848</v>
       </c>
       <c r="N49">
-        <v>-8.957287200000001</v>
+        <v>-9.186484800000002</v>
       </c>
       <c r="O49">
-        <v>-2.866331904</v>
+        <v>-2.939675136000001</v>
       </c>
       <c r="P49">
-        <v>-6.090955296000001</v>
+        <v>-6.246809664000001</v>
       </c>
       <c r="Q49">
-        <v>-2.630955296000001</v>
+        <v>-2.786809664000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1165887755325077</v>
+        <v>0.1179500981389021</v>
       </c>
       <c r="T49">
-        <v>0.9226150505042862</v>
+        <v>0.9403576476293686</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05391612655852694</v>
+        <v>0.05279287392189096</v>
       </c>
       <c r="W49">
-        <v>0.2230865773574993</v>
+        <v>0.2233514403292181</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1684878954953967</v>
+        <v>0.1649777310059093</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1685427423902538</v>
+        <v>0.1704427423902538</v>
       </c>
       <c r="C50">
-        <v>-16.31446888130322</v>
+        <v>-17.74605528021419</v>
       </c>
       <c r="D50">
-        <v>30.14953111869677</v>
+        <v>29.68994471978581</v>
       </c>
       <c r="E50">
-        <v>29.456</v>
+        <v>30.428</v>
       </c>
       <c r="F50">
-        <v>46.656</v>
+        <v>47.628</v>
       </c>
       <c r="G50">
         <v>0.192</v>
@@ -5387,37 +5387,37 @@
         <v>1.815</v>
       </c>
       <c r="M50">
-        <v>11.0014848</v>
+        <v>11.2306824</v>
       </c>
       <c r="N50">
-        <v>-9.186484800000001</v>
+        <v>-9.415682400000001</v>
       </c>
       <c r="O50">
-        <v>-2.939675136</v>
+        <v>-3.013018368</v>
       </c>
       <c r="P50">
-        <v>-6.246809664000001</v>
+        <v>-6.402664032000001</v>
       </c>
       <c r="Q50">
-        <v>-2.786809664000001</v>
+        <v>-2.942664032000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1179500981389021</v>
+        <v>0.1193648059455473</v>
       </c>
       <c r="T50">
-        <v>0.9403576476293686</v>
+        <v>0.9587960328770032</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05279287392189096</v>
+        <v>0.05171546833164829</v>
       </c>
       <c r="W50">
-        <v>0.2233514403292181</v>
+        <v>0.2236054925673973</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1649777310059093</v>
+        <v>0.1616108385364009</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1704427423902538</v>
+        <v>0.1723427423902538</v>
       </c>
       <c r="C51">
-        <v>-17.74605528021419</v>
+        <v>-19.16384058486346</v>
       </c>
       <c r="D51">
-        <v>29.68994471978581</v>
+        <v>29.24415941513654</v>
       </c>
       <c r="E51">
-        <v>30.428</v>
+        <v>31.4</v>
       </c>
       <c r="F51">
-        <v>47.628</v>
+        <v>48.6</v>
       </c>
       <c r="G51">
         <v>0.192</v>
@@ -5469,37 +5469,37 @@
         <v>1.815</v>
       </c>
       <c r="M51">
-        <v>11.2306824</v>
+        <v>11.45988</v>
       </c>
       <c r="N51">
-        <v>-9.415682400000001</v>
+        <v>-9.644880000000001</v>
       </c>
       <c r="O51">
-        <v>-3.013018368</v>
+        <v>-3.0863616</v>
       </c>
       <c r="P51">
-        <v>-6.402664032000001</v>
+        <v>-6.558518400000001</v>
       </c>
       <c r="Q51">
-        <v>-2.942664032000001</v>
+        <v>-3.098518400000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1193648059455473</v>
+        <v>0.1208361020644582</v>
       </c>
       <c r="T51">
-        <v>0.9587960328770032</v>
+        <v>0.9779719535345434</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05171546833164829</v>
+        <v>0.05068115896501532</v>
       </c>
       <c r="W51">
-        <v>0.2236054925673973</v>
+        <v>0.2238493827160494</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1616108385364009</v>
+        <v>0.1583786217656729</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1723427423902538</v>
+        <v>0.1742427423902538</v>
       </c>
       <c r="C52">
-        <v>-19.16384058486346</v>
+        <v>-20.56843725677145</v>
       </c>
       <c r="D52">
-        <v>29.24415941513654</v>
+        <v>28.81156274322855</v>
       </c>
       <c r="E52">
-        <v>31.4</v>
+        <v>32.372</v>
       </c>
       <c r="F52">
-        <v>48.6</v>
+        <v>49.572</v>
       </c>
       <c r="G52">
         <v>0.192</v>
@@ -5551,37 +5551,37 @@
         <v>1.815</v>
       </c>
       <c r="M52">
-        <v>11.45988</v>
+        <v>11.6890776</v>
       </c>
       <c r="N52">
-        <v>-9.644880000000001</v>
+        <v>-9.874077600000001</v>
       </c>
       <c r="O52">
-        <v>-3.0863616</v>
+        <v>-3.159704832000001</v>
       </c>
       <c r="P52">
-        <v>-6.558518400000001</v>
+        <v>-6.714372768</v>
       </c>
       <c r="Q52">
-        <v>-3.098518400000001</v>
+        <v>-3.254372768000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1208361020644582</v>
+        <v>0.1223674510861819</v>
       </c>
       <c r="T52">
-        <v>0.9779719535345434</v>
+        <v>0.9979305648311667</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05068115896501532</v>
+        <v>0.04968741075001502</v>
       </c>
       <c r="W52">
-        <v>0.2238493827160494</v>
+        <v>0.2240837085451465</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1583786217656729</v>
+        <v>0.155273158593797</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1742427423902538</v>
+        <v>0.1761427423902538</v>
       </c>
       <c r="C53">
-        <v>-20.56843725677145</v>
+        <v>-21.96042204616796</v>
       </c>
       <c r="D53">
-        <v>28.81156274322855</v>
+        <v>28.39157795383204</v>
       </c>
       <c r="E53">
-        <v>32.372</v>
+        <v>33.34400000000001</v>
       </c>
       <c r="F53">
-        <v>49.572</v>
+        <v>50.544</v>
       </c>
       <c r="G53">
         <v>0.192</v>
@@ -5633,37 +5633,37 @@
         <v>1.815</v>
       </c>
       <c r="M53">
-        <v>11.6890776</v>
+        <v>11.9182752</v>
       </c>
       <c r="N53">
-        <v>-9.874077600000001</v>
+        <v>-10.1032752</v>
       </c>
       <c r="O53">
-        <v>-3.159704832000001</v>
+        <v>-3.233048064000001</v>
       </c>
       <c r="P53">
-        <v>-6.714372768</v>
+        <v>-6.870227136000001</v>
       </c>
       <c r="Q53">
-        <v>-3.254372768000001</v>
+        <v>-3.410227136000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1223674510861819</v>
+        <v>0.123962606317144</v>
       </c>
       <c r="T53">
-        <v>0.9979305648311667</v>
+        <v>1.018720784931816</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04968741075001502</v>
+        <v>0.04873188362020704</v>
       </c>
       <c r="W53">
-        <v>0.2240837085451465</v>
+        <v>0.2243090218423552</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.155273158593797</v>
+        <v>0.1522871363131469</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1761427423902538</v>
+        <v>0.1780427423902538</v>
       </c>
       <c r="C54">
-        <v>-21.96042204616796</v>
+        <v>-23.34033855740524</v>
       </c>
       <c r="D54">
-        <v>28.39157795383204</v>
+        <v>27.98366144259477</v>
       </c>
       <c r="E54">
-        <v>33.34400000000001</v>
+        <v>34.316</v>
       </c>
       <c r="F54">
-        <v>50.544</v>
+        <v>51.51600000000001</v>
       </c>
       <c r="G54">
         <v>0.192</v>
@@ -5715,37 +5715,37 @@
         <v>1.815</v>
       </c>
       <c r="M54">
-        <v>11.9182752</v>
+        <v>12.1474728</v>
       </c>
       <c r="N54">
-        <v>-10.1032752</v>
+        <v>-10.3324728</v>
       </c>
       <c r="O54">
-        <v>-3.233048064000001</v>
+        <v>-3.306391296000001</v>
       </c>
       <c r="P54">
-        <v>-6.870227136000001</v>
+        <v>-7.026081504</v>
       </c>
       <c r="Q54">
-        <v>-3.410227136000001</v>
+        <v>-3.566081504</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.123962606317144</v>
+        <v>0.1256256404941045</v>
       </c>
       <c r="T54">
-        <v>1.018720784931816</v>
+        <v>1.040395695249514</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04873188362020704</v>
+        <v>0.04781241411793898</v>
       </c>
       <c r="W54">
-        <v>0.2243090218423552</v>
+        <v>0.22452583275099</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1522871363131469</v>
+        <v>0.1494137941185594</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1780427423902538</v>
+        <v>0.1799427423902538</v>
       </c>
       <c r="C55">
-        <v>-23.34033855740524</v>
+        <v>-24.70869959635171</v>
       </c>
       <c r="D55">
-        <v>27.98366144259477</v>
+        <v>27.58730040364829</v>
       </c>
       <c r="E55">
-        <v>34.316</v>
+        <v>35.28800000000001</v>
       </c>
       <c r="F55">
-        <v>51.51600000000001</v>
+        <v>52.48800000000001</v>
       </c>
       <c r="G55">
         <v>0.192</v>
@@ -5797,37 +5797,37 @@
         <v>1.815</v>
       </c>
       <c r="M55">
-        <v>12.1474728</v>
+        <v>12.3766704</v>
       </c>
       <c r="N55">
-        <v>-10.3324728</v>
+        <v>-10.5616704</v>
       </c>
       <c r="O55">
-        <v>-3.306391296000001</v>
+        <v>-3.379734528000001</v>
       </c>
       <c r="P55">
-        <v>-7.026081504</v>
+        <v>-7.181935872000002</v>
       </c>
       <c r="Q55">
-        <v>-3.566081504</v>
+        <v>-3.721935872000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1256256404941045</v>
+        <v>0.1273609805048459</v>
       </c>
       <c r="T55">
-        <v>1.040395695249514</v>
+        <v>1.06301299297233</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04781241411793898</v>
+        <v>0.04692699904168086</v>
       </c>
       <c r="W55">
-        <v>0.22452583275099</v>
+        <v>0.2247346136259717</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1494137941185594</v>
+        <v>0.1466468720052526</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1799427423902538</v>
+        <v>0.1818427423902538</v>
       </c>
       <c r="C56">
-        <v>-24.70869959635171</v>
+        <v>-26.06598932108081</v>
       </c>
       <c r="D56">
-        <v>27.58730040364829</v>
+        <v>27.2020106789192</v>
       </c>
       <c r="E56">
-        <v>35.28800000000001</v>
+        <v>36.26000000000001</v>
       </c>
       <c r="F56">
-        <v>52.48800000000001</v>
+        <v>53.46000000000001</v>
       </c>
       <c r="G56">
         <v>0.192</v>
@@ -5879,37 +5879,37 @@
         <v>1.815</v>
       </c>
       <c r="M56">
-        <v>12.3766704</v>
+        <v>12.605868</v>
       </c>
       <c r="N56">
-        <v>-10.5616704</v>
+        <v>-10.790868</v>
       </c>
       <c r="O56">
-        <v>-3.379734528000001</v>
+        <v>-3.453077760000001</v>
       </c>
       <c r="P56">
-        <v>-7.181935872000002</v>
+        <v>-7.337790240000002</v>
       </c>
       <c r="Q56">
-        <v>-3.721935872000002</v>
+        <v>-3.877790240000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1273609805048459</v>
+        <v>0.1291734467382869</v>
       </c>
       <c r="T56">
-        <v>1.06301299297233</v>
+        <v>1.086635503927271</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04692699904168086</v>
+        <v>0.04607378087728665</v>
       </c>
       <c r="W56">
-        <v>0.2247346136259717</v>
+        <v>0.2249358024691358</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1466468720052526</v>
+        <v>0.1439805652415208</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1818427423902538</v>
+        <v>0.1837427423902538</v>
       </c>
       <c r="C57">
-        <v>-26.06598932108081</v>
+        <v>-27.41266521482031</v>
       </c>
       <c r="D57">
-        <v>27.2020106789192</v>
+        <v>26.8273347851797</v>
       </c>
       <c r="E57">
-        <v>36.26000000000001</v>
+        <v>37.23200000000001</v>
       </c>
       <c r="F57">
-        <v>53.46000000000001</v>
+        <v>54.43200000000001</v>
       </c>
       <c r="G57">
         <v>0.192</v>
@@ -5961,37 +5961,37 @@
         <v>1.815</v>
       </c>
       <c r="M57">
-        <v>12.605868</v>
+        <v>12.8350656</v>
       </c>
       <c r="N57">
-        <v>-10.790868</v>
+        <v>-11.0200656</v>
       </c>
       <c r="O57">
-        <v>-3.453077760000001</v>
+        <v>-3.526420992000001</v>
       </c>
       <c r="P57">
-        <v>-7.337790240000002</v>
+        <v>-7.493644608000002</v>
       </c>
       <c r="Q57">
-        <v>-3.877790240000002</v>
+        <v>-4.033644608000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1291734467382869</v>
+        <v>0.1310682978005207</v>
       </c>
       <c r="T57">
-        <v>1.086635503927271</v>
+        <v>1.111331765380163</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04607378087728665</v>
+        <v>0.04525103479019225</v>
       </c>
       <c r="W57">
-        <v>0.2249358024691358</v>
+        <v>0.2251298059964727</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1439805652415208</v>
+        <v>0.1414094837193508</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1837427423902538</v>
+        <v>0.1856427423902539</v>
       </c>
       <c r="C58">
-        <v>-27.41266521482031</v>
+        <v>-28.7491598980667</v>
       </c>
       <c r="D58">
-        <v>26.8273347851797</v>
+        <v>26.46284010193331</v>
       </c>
       <c r="E58">
-        <v>37.23200000000001</v>
+        <v>38.20400000000001</v>
       </c>
       <c r="F58">
-        <v>54.43200000000001</v>
+        <v>55.40400000000001</v>
       </c>
       <c r="G58">
         <v>0.192</v>
@@ -6043,37 +6043,37 @@
         <v>1.815</v>
       </c>
       <c r="M58">
-        <v>12.8350656</v>
+        <v>13.0642632</v>
       </c>
       <c r="N58">
-        <v>-11.0200656</v>
+        <v>-11.2492632</v>
       </c>
       <c r="O58">
-        <v>-3.526420992000001</v>
+        <v>-3.599764224000001</v>
       </c>
       <c r="P58">
-        <v>-7.493644608000002</v>
+        <v>-7.649498976000002</v>
       </c>
       <c r="Q58">
-        <v>-4.033644608000002</v>
+        <v>-4.189498976000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1310682978005207</v>
+        <v>0.1330512814703003</v>
       </c>
       <c r="T58">
-        <v>1.111331765380163</v>
+        <v>1.137176690156446</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04525103479019225</v>
+        <v>0.04445715698685554</v>
       </c>
       <c r="W58">
-        <v>0.2251298059964727</v>
+        <v>0.2253170023824995</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1414094837193508</v>
+        <v>0.1389286155839236</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1856427423902539</v>
+        <v>0.1875427423902538</v>
       </c>
       <c r="C59">
-        <v>-28.7491598980667</v>
+        <v>-30.07588279495578</v>
       </c>
       <c r="D59">
-        <v>26.46284010193331</v>
+        <v>26.10811720504423</v>
       </c>
       <c r="E59">
-        <v>38.20400000000001</v>
+        <v>39.17600000000002</v>
       </c>
       <c r="F59">
-        <v>55.40400000000001</v>
+        <v>56.37600000000001</v>
       </c>
       <c r="G59">
         <v>0.192</v>
@@ -6125,37 +6125,37 @@
         <v>1.815</v>
       </c>
       <c r="M59">
-        <v>13.0642632</v>
+        <v>13.2934608</v>
       </c>
       <c r="N59">
-        <v>-11.2492632</v>
+        <v>-11.4784608</v>
       </c>
       <c r="O59">
-        <v>-3.599764224000001</v>
+        <v>-3.673107456000001</v>
       </c>
       <c r="P59">
-        <v>-7.649498976000002</v>
+        <v>-7.805353344000003</v>
       </c>
       <c r="Q59">
-        <v>-4.189498976000002</v>
+        <v>-4.345353344000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1330512814703003</v>
+        <v>0.1351286929338788</v>
       </c>
       <c r="T59">
-        <v>1.137176690156446</v>
+        <v>1.164252325636361</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04445715698685554</v>
+        <v>0.04369065428018561</v>
       </c>
       <c r="W59">
-        <v>0.2253170023824995</v>
+        <v>0.2254977437207323</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1389286155839236</v>
+        <v>0.1365332946255801</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1875427423902538</v>
+        <v>0.1894427423902538</v>
       </c>
       <c r="C60">
-        <v>-30.07588279495576</v>
+        <v>-31.39322166738424</v>
       </c>
       <c r="D60">
-        <v>26.10811720504424</v>
+        <v>25.76277833261576</v>
       </c>
       <c r="E60">
-        <v>39.176</v>
+        <v>40.148</v>
       </c>
       <c r="F60">
-        <v>56.376</v>
+        <v>57.348</v>
       </c>
       <c r="G60">
         <v>0.192</v>
@@ -6207,37 +6207,37 @@
         <v>1.815</v>
       </c>
       <c r="M60">
-        <v>13.2934608</v>
+        <v>13.5226584</v>
       </c>
       <c r="N60">
-        <v>-11.4784608</v>
+        <v>-11.7076584</v>
       </c>
       <c r="O60">
-        <v>-3.673107456</v>
+        <v>-3.746450688</v>
       </c>
       <c r="P60">
-        <v>-7.805353344</v>
+        <v>-7.961207712000001</v>
       </c>
       <c r="Q60">
-        <v>-4.345353344</v>
+        <v>-4.501207712000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1351286929338788</v>
+        <v>0.1373074415420222</v>
       </c>
       <c r="T60">
-        <v>1.164252325636361</v>
+        <v>1.192648723822614</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04369065428018563</v>
+        <v>0.04295013471611468</v>
       </c>
       <c r="W60">
-        <v>0.2254977437207323</v>
+        <v>0.2256723582339402</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1365332946255801</v>
+        <v>0.1342191709878584</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1894427423902538</v>
+        <v>0.1913427423902538</v>
       </c>
       <c r="C61">
-        <v>-31.39322166738424</v>
+        <v>-32.70154402896733</v>
       </c>
       <c r="D61">
-        <v>25.76277833261576</v>
+        <v>25.42645597103267</v>
       </c>
       <c r="E61">
-        <v>40.148</v>
+        <v>41.12</v>
       </c>
       <c r="F61">
-        <v>57.348</v>
+        <v>58.32</v>
       </c>
       <c r="G61">
         <v>0.192</v>
@@ -6289,37 +6289,37 @@
         <v>1.815</v>
       </c>
       <c r="M61">
-        <v>13.5226584</v>
+        <v>13.751856</v>
       </c>
       <c r="N61">
-        <v>-11.7076584</v>
+        <v>-11.936856</v>
       </c>
       <c r="O61">
-        <v>-3.746450688</v>
+        <v>-3.81979392</v>
       </c>
       <c r="P61">
-        <v>-7.961207712000001</v>
+        <v>-8.11706208</v>
       </c>
       <c r="Q61">
-        <v>-4.501207712000001</v>
+        <v>-4.65706208</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1373074415420222</v>
+        <v>0.1395951275805728</v>
       </c>
       <c r="T61">
-        <v>1.192648723822614</v>
+        <v>1.222464941918179</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04295013471611468</v>
+        <v>0.04223429913751277</v>
       </c>
       <c r="W61">
-        <v>0.2256723582339402</v>
+        <v>0.2258411522633745</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1342191709878584</v>
+        <v>0.1319821848047275</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1913427423902538</v>
+        <v>0.1932427423902538</v>
       </c>
       <c r="C62">
-        <v>-32.70154402896733</v>
+        <v>-34.00119844967185</v>
       </c>
       <c r="D62">
-        <v>25.42645597103267</v>
+        <v>25.09880155032816</v>
       </c>
       <c r="E62">
-        <v>41.12</v>
+        <v>42.092</v>
       </c>
       <c r="F62">
-        <v>58.32</v>
+        <v>59.292</v>
       </c>
       <c r="G62">
         <v>0.192</v>
@@ -6371,37 +6371,37 @@
         <v>1.815</v>
       </c>
       <c r="M62">
-        <v>13.751856</v>
+        <v>13.9810536</v>
       </c>
       <c r="N62">
-        <v>-11.936856</v>
+        <v>-12.1660536</v>
       </c>
       <c r="O62">
-        <v>-3.81979392</v>
+        <v>-3.893137152</v>
       </c>
       <c r="P62">
-        <v>-8.11706208</v>
+        <v>-8.272916448</v>
       </c>
       <c r="Q62">
-        <v>-4.65706208</v>
+        <v>-4.812916448</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1395951275805728</v>
+        <v>0.1420001308518695</v>
       </c>
       <c r="T62">
-        <v>1.222464941918179</v>
+        <v>1.253810196839158</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04223429913751277</v>
+        <v>0.04154193357788142</v>
       </c>
       <c r="W62">
-        <v>0.2258411522633745</v>
+        <v>0.2260044120623356</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1319821848047275</v>
+        <v>0.1298185424308794</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1932427423902538</v>
+        <v>0.1951427423902538</v>
       </c>
       <c r="C63">
-        <v>-34.00119844967185</v>
+        <v>-35.29251576086067</v>
       </c>
       <c r="D63">
-        <v>25.09880155032816</v>
+        <v>24.77948423913933</v>
       </c>
       <c r="E63">
-        <v>42.092</v>
+        <v>43.06400000000001</v>
       </c>
       <c r="F63">
-        <v>59.292</v>
+        <v>60.264</v>
       </c>
       <c r="G63">
         <v>0.192</v>
@@ -6453,37 +6453,37 @@
         <v>1.815</v>
       </c>
       <c r="M63">
-        <v>13.9810536</v>
+        <v>14.2102512</v>
       </c>
       <c r="N63">
-        <v>-12.1660536</v>
+        <v>-12.3952512</v>
       </c>
       <c r="O63">
-        <v>-3.893137152</v>
+        <v>-3.966480384000001</v>
       </c>
       <c r="P63">
-        <v>-8.272916448</v>
+        <v>-8.428770816000002</v>
       </c>
       <c r="Q63">
-        <v>-4.812916448</v>
+        <v>-4.968770816000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1420001308518695</v>
+        <v>0.1445317132427082</v>
       </c>
       <c r="T63">
-        <v>1.253810196839158</v>
+        <v>1.286805202019136</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04154193357788142</v>
+        <v>0.04087190239114139</v>
       </c>
       <c r="W63">
-        <v>0.2260044120623356</v>
+        <v>0.2261624054161689</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1298185424308794</v>
+        <v>0.1277246949723169</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1951427423902538</v>
+        <v>0.1970427423902538</v>
       </c>
       <c r="C64">
-        <v>-35.29251576086067</v>
+        <v>-36.57581016950662</v>
       </c>
       <c r="D64">
-        <v>24.77948423913933</v>
+        <v>24.46818983049338</v>
       </c>
       <c r="E64">
-        <v>43.06400000000001</v>
+        <v>44.036</v>
       </c>
       <c r="F64">
-        <v>60.264</v>
+        <v>61.236</v>
       </c>
       <c r="G64">
         <v>0.192</v>
@@ -6535,37 +6535,37 @@
         <v>1.815</v>
       </c>
       <c r="M64">
-        <v>14.2102512</v>
+        <v>14.4394488</v>
       </c>
       <c r="N64">
-        <v>-12.3952512</v>
+        <v>-12.6244488</v>
       </c>
       <c r="O64">
-        <v>-3.966480384000001</v>
+        <v>-4.039823616000001</v>
       </c>
       <c r="P64">
-        <v>-8.428770816000002</v>
+        <v>-8.584625184</v>
       </c>
       <c r="Q64">
-        <v>-4.968770816000002</v>
+        <v>-5.124625184</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1445317132427082</v>
+        <v>0.1472001379249435</v>
       </c>
       <c r="T64">
-        <v>1.286805202019136</v>
+        <v>1.321583720992626</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04087190239114139</v>
+        <v>0.04022314203572645</v>
       </c>
       <c r="W64">
-        <v>0.2261624054161689</v>
+        <v>0.2263153831079757</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1277246949723169</v>
+        <v>0.1256973188616451</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1970427423902538</v>
+        <v>0.1989427423902538</v>
       </c>
       <c r="C65">
-        <v>-36.57581016950662</v>
+        <v>-37.85138028946352</v>
       </c>
       <c r="D65">
-        <v>24.46818983049338</v>
+        <v>24.16461971053648</v>
       </c>
       <c r="E65">
-        <v>44.036</v>
+        <v>45.00800000000001</v>
       </c>
       <c r="F65">
-        <v>61.236</v>
+        <v>62.20800000000001</v>
       </c>
       <c r="G65">
         <v>0.192</v>
@@ -6617,37 +6617,37 @@
         <v>1.815</v>
       </c>
       <c r="M65">
-        <v>14.4394488</v>
+        <v>14.6686464</v>
       </c>
       <c r="N65">
-        <v>-12.6244488</v>
+        <v>-12.8536464</v>
       </c>
       <c r="O65">
-        <v>-4.039823616000001</v>
+        <v>-4.113166848000001</v>
       </c>
       <c r="P65">
-        <v>-8.584625184</v>
+        <v>-8.740479552000002</v>
       </c>
       <c r="Q65">
-        <v>-5.124625184</v>
+        <v>-5.280479552000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1472001379249435</v>
+        <v>0.1500168084228586</v>
       </c>
       <c r="T65">
-        <v>1.321583720992626</v>
+        <v>1.358294379909088</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04022314203572645</v>
+        <v>0.03959465544141822</v>
       </c>
       <c r="W65">
-        <v>0.2263153831079757</v>
+        <v>0.2264635802469136</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1256973188616451</v>
+        <v>0.1237332982544319</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1989427423902538</v>
+        <v>0.2008427423902538</v>
       </c>
       <c r="C66">
-        <v>-37.85138028946352</v>
+        <v>-39.11951009691012</v>
       </c>
       <c r="D66">
-        <v>24.16461971053648</v>
+        <v>23.86848990308988</v>
       </c>
       <c r="E66">
-        <v>45.00800000000001</v>
+        <v>45.98</v>
       </c>
       <c r="F66">
-        <v>62.20800000000001</v>
+        <v>63.18000000000001</v>
       </c>
       <c r="G66">
         <v>0.192</v>
@@ -6699,37 +6699,37 @@
         <v>1.815</v>
       </c>
       <c r="M66">
-        <v>14.6686464</v>
+        <v>14.897844</v>
       </c>
       <c r="N66">
-        <v>-12.8536464</v>
+        <v>-13.082844</v>
       </c>
       <c r="O66">
-        <v>-4.113166848000001</v>
+        <v>-4.186510080000001</v>
       </c>
       <c r="P66">
-        <v>-8.740479552000002</v>
+        <v>-8.896333920000002</v>
       </c>
       <c r="Q66">
-        <v>-5.280479552000002</v>
+        <v>-5.436333920000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1500168084228586</v>
+        <v>0.1529944315206546</v>
       </c>
       <c r="T66">
-        <v>1.358294379909088</v>
+        <v>1.397102790763634</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03959465544141822</v>
+        <v>0.03898550689616563</v>
       </c>
       <c r="W66">
-        <v>0.2264635802469136</v>
+        <v>0.2266072174738842</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1237332982544319</v>
+        <v>0.1218297090505176</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2008427423902538</v>
+        <v>0.2027427423902538</v>
       </c>
       <c r="C67">
-        <v>-39.11951009691012</v>
+        <v>-40.38046981639242</v>
       </c>
       <c r="D67">
-        <v>23.86848990308988</v>
+        <v>23.57953018360758</v>
       </c>
       <c r="E67">
-        <v>45.98</v>
+        <v>46.952</v>
       </c>
       <c r="F67">
-        <v>63.18000000000001</v>
+        <v>64.152</v>
       </c>
       <c r="G67">
         <v>0.192</v>
@@ -6781,37 +6781,37 @@
         <v>1.815</v>
       </c>
       <c r="M67">
-        <v>14.897844</v>
+        <v>15.1270416</v>
       </c>
       <c r="N67">
-        <v>-13.082844</v>
+        <v>-13.3120416</v>
       </c>
       <c r="O67">
-        <v>-4.186510080000001</v>
+        <v>-4.259853312000001</v>
       </c>
       <c r="P67">
-        <v>-8.896333920000002</v>
+        <v>-9.052188288</v>
       </c>
       <c r="Q67">
-        <v>-5.436333920000002</v>
+        <v>-5.592188288</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1529944315206546</v>
+        <v>0.1561472089183209</v>
       </c>
       <c r="T67">
-        <v>1.397102790763634</v>
+        <v>1.438194049315505</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03898550689616563</v>
+        <v>0.03839481739773889</v>
       </c>
       <c r="W67">
-        <v>0.2266072174738842</v>
+        <v>0.2267465020576132</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1218297090505176</v>
+        <v>0.119983804367934</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2027427423902538</v>
+        <v>0.2046427423902538</v>
       </c>
       <c r="C68">
-        <v>-40.38046981639242</v>
+        <v>-41.63451674327553</v>
       </c>
       <c r="D68">
-        <v>23.57953018360758</v>
+        <v>23.29748325672448</v>
       </c>
       <c r="E68">
-        <v>46.952</v>
+        <v>47.92400000000001</v>
       </c>
       <c r="F68">
-        <v>64.152</v>
+        <v>65.12400000000001</v>
       </c>
       <c r="G68">
         <v>0.192</v>
@@ -6863,37 +6863,37 @@
         <v>1.815</v>
       </c>
       <c r="M68">
-        <v>15.1270416</v>
+        <v>15.3562392</v>
       </c>
       <c r="N68">
-        <v>-13.3120416</v>
+        <v>-13.5412392</v>
       </c>
       <c r="O68">
-        <v>-4.259853312000001</v>
+        <v>-4.333196544000002</v>
       </c>
       <c r="P68">
-        <v>-9.052188288</v>
+        <v>-9.208042656000002</v>
       </c>
       <c r="Q68">
-        <v>-5.592188288</v>
+        <v>-5.748042656000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1561472089183209</v>
+        <v>0.1594910637340276</v>
       </c>
       <c r="T68">
-        <v>1.438194049315505</v>
+        <v>1.481775687173551</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03839481739773889</v>
+        <v>0.03782176042165322</v>
       </c>
       <c r="W68">
-        <v>0.2267465020576132</v>
+        <v>0.2268816288925742</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.119983804367934</v>
+        <v>0.1181930013176663</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2046427423902538</v>
+        <v>0.2065427423902538</v>
       </c>
       <c r="C69">
-        <v>-41.63451674327553</v>
+        <v>-42.88189600786657</v>
       </c>
       <c r="D69">
-        <v>23.29748325672448</v>
+        <v>23.02210399213343</v>
       </c>
       <c r="E69">
-        <v>47.92400000000001</v>
+        <v>48.896</v>
       </c>
       <c r="F69">
-        <v>65.12400000000001</v>
+        <v>66.096</v>
       </c>
       <c r="G69">
         <v>0.192</v>
@@ -6945,37 +6945,37 @@
         <v>1.815</v>
       </c>
       <c r="M69">
-        <v>15.3562392</v>
+        <v>15.5854368</v>
       </c>
       <c r="N69">
-        <v>-13.5412392</v>
+        <v>-13.7704368</v>
       </c>
       <c r="O69">
-        <v>-4.333196544000002</v>
+        <v>-4.406539776000001</v>
       </c>
       <c r="P69">
-        <v>-9.208042656000002</v>
+        <v>-9.363897024000002</v>
       </c>
       <c r="Q69">
-        <v>-5.748042656000002</v>
+        <v>-5.903897024000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1594910637340276</v>
+        <v>0.163043909475716</v>
       </c>
       <c r="T69">
-        <v>1.481775687173551</v>
+        <v>1.528081177397724</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03782176042165322</v>
+        <v>0.03726555806251126</v>
       </c>
       <c r="W69">
-        <v>0.2268816288925742</v>
+        <v>0.2270127814088598</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1181930013176663</v>
+        <v>0.1164548689453477</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2065427423902538</v>
+        <v>0.2084427423902538</v>
       </c>
       <c r="C70">
-        <v>-42.88189600786657</v>
+        <v>-44.12284128597863</v>
       </c>
       <c r="D70">
-        <v>23.02210399213343</v>
+        <v>22.75315871402138</v>
       </c>
       <c r="E70">
-        <v>48.896</v>
+        <v>49.86800000000001</v>
       </c>
       <c r="F70">
-        <v>66.096</v>
+        <v>67.06800000000001</v>
       </c>
       <c r="G70">
         <v>0.192</v>
@@ -7027,37 +7027,37 @@
         <v>1.815</v>
       </c>
       <c r="M70">
-        <v>15.5854368</v>
+        <v>15.8146344</v>
       </c>
       <c r="N70">
-        <v>-13.7704368</v>
+        <v>-13.9996344</v>
       </c>
       <c r="O70">
-        <v>-4.406539776000001</v>
+        <v>-4.479883008000001</v>
       </c>
       <c r="P70">
-        <v>-9.363897024000002</v>
+        <v>-9.519751392000003</v>
       </c>
       <c r="Q70">
-        <v>-5.903897024000002</v>
+        <v>-6.059751392000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.163043909475716</v>
+        <v>0.1668259710717068</v>
       </c>
       <c r="T70">
-        <v>1.528081177397724</v>
+        <v>1.577374118604103</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03726555806251126</v>
+        <v>0.03672547751088067</v>
       </c>
       <c r="W70">
-        <v>0.2270127814088598</v>
+        <v>0.2271401324029343</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1164548689453477</v>
+        <v>0.1147671172215021</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2084427423902538</v>
+        <v>0.2103427423902538</v>
       </c>
       <c r="C71">
-        <v>-44.12284128597863</v>
+        <v>-45.35757546026451</v>
       </c>
       <c r="D71">
-        <v>22.75315871402138</v>
+        <v>22.4904245397355</v>
       </c>
       <c r="E71">
-        <v>49.86800000000001</v>
+        <v>50.84</v>
       </c>
       <c r="F71">
-        <v>67.06800000000001</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="G71">
         <v>0.192</v>
@@ -7109,37 +7109,37 @@
         <v>1.815</v>
       </c>
       <c r="M71">
-        <v>15.8146344</v>
+        <v>16.043832</v>
       </c>
       <c r="N71">
-        <v>-13.9996344</v>
+        <v>-14.228832</v>
       </c>
       <c r="O71">
-        <v>-4.479883008000001</v>
+        <v>-4.553226240000001</v>
       </c>
       <c r="P71">
-        <v>-9.519751392000003</v>
+        <v>-9.675605760000002</v>
       </c>
       <c r="Q71">
-        <v>-6.059751392000003</v>
+        <v>-6.215605760000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1668259710717068</v>
+        <v>0.1708601701074304</v>
       </c>
       <c r="T71">
-        <v>1.577374118604103</v>
+        <v>1.629953255890906</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03672547751088067</v>
+        <v>0.0362008278321538</v>
       </c>
       <c r="W71">
-        <v>0.2271401324029343</v>
+        <v>0.2272638447971781</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1147671172215021</v>
+        <v>0.1131275869754806</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2103427423902538</v>
+        <v>0.2122427423902538</v>
       </c>
       <c r="C72">
-        <v>-45.35757546026451</v>
+        <v>-46.58631123625472</v>
       </c>
       <c r="D72">
-        <v>22.4904245397355</v>
+        <v>22.2336887637453</v>
       </c>
       <c r="E72">
-        <v>50.84</v>
+        <v>51.81200000000001</v>
       </c>
       <c r="F72">
-        <v>68.04000000000001</v>
+        <v>69.01200000000001</v>
       </c>
       <c r="G72">
         <v>0.192</v>
@@ -7191,37 +7191,37 @@
         <v>1.815</v>
       </c>
       <c r="M72">
-        <v>16.043832</v>
+        <v>16.2730296</v>
       </c>
       <c r="N72">
-        <v>-14.228832</v>
+        <v>-14.45802960000001</v>
       </c>
       <c r="O72">
-        <v>-4.553226240000001</v>
+        <v>-4.626569472000002</v>
       </c>
       <c r="P72">
-        <v>-9.675605760000002</v>
+        <v>-9.831460128000003</v>
       </c>
       <c r="Q72">
-        <v>-6.215605760000002</v>
+        <v>-6.371460128000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1708601701074304</v>
+        <v>0.1751725897663073</v>
       </c>
       <c r="T72">
-        <v>1.629953255890906</v>
+        <v>1.686158540576799</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0362008278321538</v>
+        <v>0.03569095701761642</v>
       </c>
       <c r="W72">
-        <v>0.2272638447971781</v>
+        <v>0.2273840723352461</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1131275869754806</v>
+        <v>0.1115342406800514</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2122427423902538</v>
+        <v>0.2141427423902538</v>
       </c>
       <c r="C73">
-        <v>-46.5863112362547</v>
+        <v>-47.80925171667758</v>
       </c>
       <c r="D73">
-        <v>22.2336887637453</v>
+        <v>21.98274828332242</v>
       </c>
       <c r="E73">
-        <v>51.812</v>
+        <v>52.78399999999999</v>
       </c>
       <c r="F73">
-        <v>69.012</v>
+        <v>69.98399999999999</v>
       </c>
       <c r="G73">
         <v>0.192</v>
@@ -7273,37 +7273,37 @@
         <v>1.815</v>
       </c>
       <c r="M73">
-        <v>16.2730296</v>
+        <v>16.5022272</v>
       </c>
       <c r="N73">
-        <v>-14.4580296</v>
+        <v>-14.6872272</v>
       </c>
       <c r="O73">
-        <v>-4.626569472000001</v>
+        <v>-4.699912704</v>
       </c>
       <c r="P73">
-        <v>-9.831460128</v>
+        <v>-9.987314496</v>
       </c>
       <c r="Q73">
-        <v>-6.371460128</v>
+        <v>-6.527314496</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1751725897663073</v>
+        <v>0.1797930394008183</v>
       </c>
       <c r="T73">
-        <v>1.686158540576799</v>
+        <v>1.746378488454542</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03569095701761642</v>
+        <v>0.03519524928126064</v>
       </c>
       <c r="W73">
-        <v>0.2273840723352461</v>
+        <v>0.2275009602194788</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1115342406800514</v>
+        <v>0.1099851540039395</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2141427423902538</v>
+        <v>0.2160427423902538</v>
       </c>
       <c r="C74">
-        <v>-47.80925171667758</v>
+        <v>-49.02659093732153</v>
       </c>
       <c r="D74">
-        <v>21.98274828332242</v>
+        <v>21.73740906267847</v>
       </c>
       <c r="E74">
-        <v>52.78399999999999</v>
+        <v>53.756</v>
       </c>
       <c r="F74">
-        <v>69.98399999999999</v>
+        <v>70.956</v>
       </c>
       <c r="G74">
         <v>0.192</v>
@@ -7355,37 +7355,37 @@
         <v>1.815</v>
       </c>
       <c r="M74">
-        <v>16.5022272</v>
+        <v>16.7314248</v>
       </c>
       <c r="N74">
-        <v>-14.6872272</v>
+        <v>-14.9164248</v>
       </c>
       <c r="O74">
-        <v>-4.699912704</v>
+        <v>-4.773255936000001</v>
       </c>
       <c r="P74">
-        <v>-9.987314496</v>
+        <v>-10.143168864</v>
       </c>
       <c r="Q74">
-        <v>-6.527314496</v>
+        <v>-6.683168864000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1797930394008183</v>
+        <v>0.1847557445638115</v>
       </c>
       <c r="T74">
-        <v>1.746378488454542</v>
+        <v>1.811059173212117</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03519524928126064</v>
+        <v>0.03471312257877762</v>
       </c>
       <c r="W74">
-        <v>0.2275009602194788</v>
+        <v>0.2276146456959243</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1099851540039395</v>
+        <v>0.1084785080586801</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2160427423902538</v>
+        <v>0.2179427423902538</v>
       </c>
       <c r="C75">
-        <v>-49.02659093732153</v>
+        <v>-50.23851436740989</v>
       </c>
       <c r="D75">
-        <v>21.73740906267847</v>
+        <v>21.49748563259011</v>
       </c>
       <c r="E75">
-        <v>53.756</v>
+        <v>54.72799999999999</v>
       </c>
       <c r="F75">
-        <v>70.956</v>
+        <v>71.928</v>
       </c>
       <c r="G75">
         <v>0.192</v>
@@ -7437,37 +7437,37 @@
         <v>1.815</v>
       </c>
       <c r="M75">
-        <v>16.7314248</v>
+        <v>16.9606224</v>
       </c>
       <c r="N75">
-        <v>-14.9164248</v>
+        <v>-15.1456224</v>
       </c>
       <c r="O75">
-        <v>-4.773255936000001</v>
+        <v>-4.846599168</v>
       </c>
       <c r="P75">
-        <v>-10.143168864</v>
+        <v>-10.299023232</v>
       </c>
       <c r="Q75">
-        <v>-6.683168864000003</v>
+        <v>-6.839023232</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1847557445638115</v>
+        <v>0.1901001962778043</v>
       </c>
       <c r="T75">
-        <v>1.811059173212117</v>
+        <v>1.880715295258737</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03471312257877762</v>
+        <v>0.03424402632771306</v>
       </c>
       <c r="W75">
-        <v>0.2276146456959243</v>
+        <v>0.2277252585919253</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1084785080586801</v>
+        <v>0.1070125822741034</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2179427423902538</v>
+        <v>0.2198427423902538</v>
       </c>
       <c r="C76">
-        <v>-50.23851436740989</v>
+        <v>-51.44519937720099</v>
       </c>
       <c r="D76">
-        <v>21.49748563259011</v>
+        <v>21.26280062279901</v>
       </c>
       <c r="E76">
-        <v>54.72799999999999</v>
+        <v>55.7</v>
       </c>
       <c r="F76">
-        <v>71.928</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G76">
         <v>0.192</v>
@@ -7519,37 +7519,37 @@
         <v>1.815</v>
       </c>
       <c r="M76">
-        <v>16.9606224</v>
+        <v>17.18982</v>
       </c>
       <c r="N76">
-        <v>-15.1456224</v>
+        <v>-15.37482</v>
       </c>
       <c r="O76">
-        <v>-4.846599168</v>
+        <v>-4.919942400000001</v>
       </c>
       <c r="P76">
-        <v>-10.299023232</v>
+        <v>-10.4548776</v>
       </c>
       <c r="Q76">
-        <v>-6.839023232</v>
+        <v>-6.9948776</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1901001962778043</v>
+        <v>0.1958722041289165</v>
       </c>
       <c r="T76">
-        <v>1.880715295258737</v>
+        <v>1.955943907069087</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03424402632771306</v>
+        <v>0.03378743931001021</v>
       </c>
       <c r="W76">
-        <v>0.2277252585919253</v>
+        <v>0.2278329218106996</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1070125822741034</v>
+        <v>0.1055857478437819</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2198427423902538</v>
+        <v>0.2217427423902538</v>
       </c>
       <c r="C77">
-        <v>-51.44519937720099</v>
+        <v>-52.64681567529021</v>
       </c>
       <c r="D77">
-        <v>21.26280062279901</v>
+        <v>21.03318432470979</v>
       </c>
       <c r="E77">
-        <v>55.7</v>
+        <v>56.672</v>
       </c>
       <c r="F77">
-        <v>72.90000000000001</v>
+        <v>73.872</v>
       </c>
       <c r="G77">
         <v>0.192</v>
@@ -7601,37 +7601,37 @@
         <v>1.815</v>
       </c>
       <c r="M77">
-        <v>17.18982</v>
+        <v>17.4190176</v>
       </c>
       <c r="N77">
-        <v>-15.37482</v>
+        <v>-15.6040176</v>
       </c>
       <c r="O77">
-        <v>-4.919942400000001</v>
+        <v>-4.993285632</v>
       </c>
       <c r="P77">
-        <v>-10.4548776</v>
+        <v>-10.610731968</v>
       </c>
       <c r="Q77">
-        <v>-6.9948776</v>
+        <v>-7.150731968</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1958722041289165</v>
+        <v>0.202125212634288</v>
       </c>
       <c r="T77">
-        <v>1.955943907069087</v>
+        <v>2.037441569863632</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03378743931001021</v>
+        <v>0.03334286774014166</v>
       </c>
       <c r="W77">
-        <v>0.2278329218106996</v>
+        <v>0.2279377517868746</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1055857478437819</v>
+        <v>0.1041964616879427</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2217427423902538</v>
+        <v>0.2236427423902538</v>
       </c>
       <c r="C78">
-        <v>-52.64681567529021</v>
+        <v>-53.84352571788084</v>
       </c>
       <c r="D78">
-        <v>21.03318432470979</v>
+        <v>20.80847428211917</v>
       </c>
       <c r="E78">
-        <v>56.672</v>
+        <v>57.64400000000001</v>
       </c>
       <c r="F78">
-        <v>73.872</v>
+        <v>74.84400000000001</v>
       </c>
       <c r="G78">
         <v>0.192</v>
@@ -7683,37 +7683,37 @@
         <v>1.815</v>
       </c>
       <c r="M78">
-        <v>17.4190176</v>
+        <v>17.6482152</v>
       </c>
       <c r="N78">
-        <v>-15.6040176</v>
+        <v>-15.8332152</v>
       </c>
       <c r="O78">
-        <v>-4.993285632</v>
+        <v>-5.066628864000001</v>
       </c>
       <c r="P78">
-        <v>-10.610731968</v>
+        <v>-10.766586336</v>
       </c>
       <c r="Q78">
-        <v>-7.150731968</v>
+        <v>-7.306586336000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.202125212634288</v>
+        <v>0.2089219610096918</v>
       </c>
       <c r="T78">
-        <v>2.037441569863632</v>
+        <v>2.12602598594466</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03334286774014166</v>
+        <v>0.03290984348377618</v>
       </c>
       <c r="W78">
-        <v>0.2279377517868746</v>
+        <v>0.2280398589065256</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1041964616879427</v>
+        <v>0.1028432608868005</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2236427423902538</v>
+        <v>0.2255427423902538</v>
       </c>
       <c r="C79">
-        <v>-53.84352571788084</v>
+        <v>-55.03548509209685</v>
       </c>
       <c r="D79">
-        <v>20.80847428211917</v>
+        <v>20.58851490790316</v>
       </c>
       <c r="E79">
-        <v>57.64400000000001</v>
+        <v>58.616</v>
       </c>
       <c r="F79">
-        <v>74.84400000000001</v>
+        <v>75.816</v>
       </c>
       <c r="G79">
         <v>0.192</v>
@@ -7765,37 +7765,37 @@
         <v>1.815</v>
       </c>
       <c r="M79">
-        <v>17.6482152</v>
+        <v>17.8774128</v>
       </c>
       <c r="N79">
-        <v>-15.8332152</v>
+        <v>-16.0624128</v>
       </c>
       <c r="O79">
-        <v>-5.066628864000001</v>
+        <v>-5.139972096000001</v>
       </c>
       <c r="P79">
-        <v>-10.766586336</v>
+        <v>-10.922440704</v>
       </c>
       <c r="Q79">
-        <v>-7.306586336000003</v>
+        <v>-7.462440704000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2089219610096918</v>
+        <v>0.2163365956010414</v>
       </c>
       <c r="T79">
-        <v>2.12602598594466</v>
+        <v>2.222663530760326</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03290984348377618</v>
+        <v>0.03248792241347136</v>
       </c>
       <c r="W79">
-        <v>0.2280398589065256</v>
+        <v>0.2281393478949035</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1028432608868005</v>
+        <v>0.1015247575420979</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2255427423902538</v>
+        <v>0.2274427423902538</v>
       </c>
       <c r="C80">
-        <v>-55.03548509209685</v>
+        <v>-56.22284287523894</v>
       </c>
       <c r="D80">
-        <v>20.58851490790316</v>
+        <v>20.37315712476107</v>
       </c>
       <c r="E80">
-        <v>58.616</v>
+        <v>59.58800000000001</v>
       </c>
       <c r="F80">
-        <v>75.816</v>
+        <v>76.78800000000001</v>
       </c>
       <c r="G80">
         <v>0.192</v>
@@ -7847,37 +7847,37 @@
         <v>1.815</v>
       </c>
       <c r="M80">
-        <v>17.8774128</v>
+        <v>18.1066104</v>
       </c>
       <c r="N80">
-        <v>-16.0624128</v>
+        <v>-16.2916104</v>
       </c>
       <c r="O80">
-        <v>-5.139972096000001</v>
+        <v>-5.213315328000001</v>
       </c>
       <c r="P80">
-        <v>-10.922440704</v>
+        <v>-11.078295072</v>
       </c>
       <c r="Q80">
-        <v>-7.462440704000003</v>
+        <v>-7.618295072000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2163365956010414</v>
+        <v>0.2244573858677577</v>
       </c>
       <c r="T80">
-        <v>2.222663530760326</v>
+        <v>2.328504651272723</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03248792241347136</v>
+        <v>0.0320766828892502</v>
       </c>
       <c r="W80">
-        <v>0.2281393478949035</v>
+        <v>0.2282363181747148</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1015247575420979</v>
+        <v>0.100239634028907</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2274427423902538</v>
+        <v>0.2293427423902538</v>
       </c>
       <c r="C81">
-        <v>-56.22284287523894</v>
+        <v>-57.405741971727</v>
       </c>
       <c r="D81">
-        <v>20.37315712476107</v>
+        <v>20.16225802827301</v>
       </c>
       <c r="E81">
-        <v>59.58800000000001</v>
+        <v>60.56</v>
       </c>
       <c r="F81">
-        <v>76.78800000000001</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="G81">
         <v>0.192</v>
@@ -7929,37 +7929,37 @@
         <v>1.815</v>
       </c>
       <c r="M81">
-        <v>18.1066104</v>
+        <v>18.335808</v>
       </c>
       <c r="N81">
-        <v>-16.2916104</v>
+        <v>-16.520808</v>
       </c>
       <c r="O81">
-        <v>-5.213315328000001</v>
+        <v>-5.286658560000001</v>
       </c>
       <c r="P81">
-        <v>-11.078295072</v>
+        <v>-11.23414944</v>
       </c>
       <c r="Q81">
-        <v>-7.618295072000003</v>
+        <v>-7.774149440000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2244573858677577</v>
+        <v>0.2333902551611456</v>
       </c>
       <c r="T81">
-        <v>2.328504651272723</v>
+        <v>2.444929883836359</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0320766828892502</v>
+        <v>0.03167572435313457</v>
       </c>
       <c r="W81">
-        <v>0.2282363181747148</v>
+        <v>0.2283308641975309</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.100239634028907</v>
+        <v>0.09898663860354562</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2293427423902538</v>
+        <v>0.2312427423902538</v>
       </c>
       <c r="C82">
-        <v>-57.405741971727</v>
+        <v>-58.58431942932899</v>
       </c>
       <c r="D82">
-        <v>20.16225802827301</v>
+        <v>19.95568057067102</v>
       </c>
       <c r="E82">
-        <v>60.56</v>
+        <v>61.53200000000001</v>
       </c>
       <c r="F82">
-        <v>77.76000000000001</v>
+        <v>78.73200000000001</v>
       </c>
       <c r="G82">
         <v>0.192</v>
@@ -8011,37 +8011,37 @@
         <v>1.815</v>
       </c>
       <c r="M82">
-        <v>18.335808</v>
+        <v>18.5650056</v>
       </c>
       <c r="N82">
-        <v>-16.520808</v>
+        <v>-16.7500056</v>
       </c>
       <c r="O82">
-        <v>-5.286658560000001</v>
+        <v>-5.360001792</v>
       </c>
       <c r="P82">
-        <v>-11.23414944</v>
+        <v>-11.390003808</v>
       </c>
       <c r="Q82">
-        <v>-7.774149440000001</v>
+        <v>-7.930003808000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2333902551611456</v>
+        <v>0.2432634264854164</v>
       </c>
       <c r="T82">
-        <v>2.444929883836359</v>
+        <v>2.573610404038273</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03167572435313457</v>
+        <v>0.03128466602778723</v>
       </c>
       <c r="W82">
-        <v>0.2283308641975309</v>
+        <v>0.2284230757506478</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09898663860354562</v>
+        <v>0.09776458133683519</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2312427423902538</v>
+        <v>0.2331427423902538</v>
       </c>
       <c r="C83">
-        <v>-58.58431942932899</v>
+        <v>-59.75870673614708</v>
       </c>
       <c r="D83">
-        <v>19.95568057067102</v>
+        <v>19.75329326385294</v>
       </c>
       <c r="E83">
-        <v>61.53200000000001</v>
+        <v>62.504</v>
       </c>
       <c r="F83">
-        <v>78.73200000000001</v>
+        <v>79.70400000000001</v>
       </c>
       <c r="G83">
         <v>0.192</v>
@@ -8093,37 +8093,37 @@
         <v>1.815</v>
       </c>
       <c r="M83">
-        <v>18.5650056</v>
+        <v>18.7942032</v>
       </c>
       <c r="N83">
-        <v>-16.7500056</v>
+        <v>-16.9792032</v>
       </c>
       <c r="O83">
-        <v>-5.360001792</v>
+        <v>-5.433345024</v>
       </c>
       <c r="P83">
-        <v>-11.390003808</v>
+        <v>-11.545858176</v>
       </c>
       <c r="Q83">
-        <v>-7.930003808000001</v>
+        <v>-8.085858175999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2432634264854164</v>
+        <v>0.2542336168457173</v>
       </c>
       <c r="T83">
-        <v>2.573610404038273</v>
+        <v>2.716588759818177</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03128466602778723</v>
+        <v>0.0309031457103752</v>
       </c>
       <c r="W83">
-        <v>0.2284230757506478</v>
+        <v>0.2285130382414935</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09776458133683519</v>
+        <v>0.09657233034492263</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2331427423902538</v>
+        <v>0.2350427423902538</v>
       </c>
       <c r="C84">
-        <v>-59.75870673614708</v>
+        <v>-60.92903009971323</v>
       </c>
       <c r="D84">
-        <v>19.75329326385294</v>
+        <v>19.55496990028679</v>
       </c>
       <c r="E84">
-        <v>62.504</v>
+        <v>63.47600000000001</v>
       </c>
       <c r="F84">
-        <v>79.70400000000001</v>
+        <v>80.67600000000002</v>
       </c>
       <c r="G84">
         <v>0.192</v>
@@ -8175,37 +8175,37 @@
         <v>1.815</v>
       </c>
       <c r="M84">
-        <v>18.7942032</v>
+        <v>19.0234008</v>
       </c>
       <c r="N84">
-        <v>-16.9792032</v>
+        <v>-17.20840080000001</v>
       </c>
       <c r="O84">
-        <v>-5.433345024</v>
+        <v>-5.506688256000002</v>
       </c>
       <c r="P84">
-        <v>-11.545858176</v>
+        <v>-11.701712544</v>
       </c>
       <c r="Q84">
-        <v>-8.085858175999999</v>
+        <v>-8.241712544000006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2542336168457173</v>
+        <v>0.2664944178366419</v>
       </c>
       <c r="T84">
-        <v>2.716588759818177</v>
+        <v>2.876388098631011</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0309031457103752</v>
+        <v>0.03053081865362368</v>
       </c>
       <c r="W84">
-        <v>0.2285130382414935</v>
+        <v>0.2286008329614755</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09657233034492263</v>
+        <v>0.09540880829257392</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2350427423902538</v>
+        <v>0.2369427423902538</v>
       </c>
       <c r="C85">
-        <v>-60.92903009971323</v>
+        <v>-62.09541070943938</v>
       </c>
       <c r="D85">
-        <v>19.55496990028679</v>
+        <v>19.36058929056063</v>
       </c>
       <c r="E85">
-        <v>63.47600000000001</v>
+        <v>64.44800000000001</v>
       </c>
       <c r="F85">
-        <v>80.67600000000002</v>
+        <v>81.64800000000001</v>
       </c>
       <c r="G85">
         <v>0.192</v>
@@ -8257,37 +8257,37 @@
         <v>1.815</v>
       </c>
       <c r="M85">
-        <v>19.0234008</v>
+        <v>19.2525984</v>
       </c>
       <c r="N85">
-        <v>-17.20840080000001</v>
+        <v>-17.43759840000001</v>
       </c>
       <c r="O85">
-        <v>-5.506688256000002</v>
+        <v>-5.580031488000002</v>
       </c>
       <c r="P85">
-        <v>-11.701712544</v>
+        <v>-11.857566912</v>
       </c>
       <c r="Q85">
-        <v>-8.241712544000006</v>
+        <v>-8.397566912000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2664944178366419</v>
+        <v>0.2802878189514321</v>
       </c>
       <c r="T85">
-        <v>2.876388098631011</v>
+        <v>3.05616235479545</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03053081865362368</v>
+        <v>0.03016735652679483</v>
       </c>
       <c r="W85">
-        <v>0.2286008329614755</v>
+        <v>0.2286865373309818</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09540880829257392</v>
+        <v>0.09427298914623372</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2369427423902538</v>
+        <v>0.2388427423902538</v>
       </c>
       <c r="C86">
-        <v>-62.09541070943935</v>
+        <v>-63.25796498356846</v>
       </c>
       <c r="D86">
-        <v>19.36058929056065</v>
+        <v>19.17003501643154</v>
       </c>
       <c r="E86">
-        <v>64.44799999999999</v>
+        <v>65.42</v>
       </c>
       <c r="F86">
-        <v>81.648</v>
+        <v>82.62</v>
       </c>
       <c r="G86">
         <v>0.192</v>
@@ -8339,37 +8339,37 @@
         <v>1.815</v>
       </c>
       <c r="M86">
-        <v>19.2525984</v>
+        <v>19.481796</v>
       </c>
       <c r="N86">
-        <v>-17.4375984</v>
+        <v>-17.66679600000001</v>
       </c>
       <c r="O86">
-        <v>-5.580031487999999</v>
+        <v>-5.653374720000001</v>
       </c>
       <c r="P86">
-        <v>-11.857566912</v>
+        <v>-12.01342128</v>
       </c>
       <c r="Q86">
-        <v>-8.397566911999998</v>
+        <v>-8.553421280000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2802878189514319</v>
+        <v>0.2959203402148607</v>
       </c>
       <c r="T86">
-        <v>3.056162354795448</v>
+        <v>3.259906511781811</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03016735652679484</v>
+        <v>0.02981244645000901</v>
       </c>
       <c r="W86">
-        <v>0.2286865373309818</v>
+        <v>0.2287702251270879</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09427298914623394</v>
+        <v>0.0931638951562781</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2388427423902538</v>
+        <v>0.2407427423902538</v>
       </c>
       <c r="C87">
-        <v>-63.25796498356846</v>
+        <v>-64.41680480168441</v>
       </c>
       <c r="D87">
-        <v>19.17003501643154</v>
+        <v>18.9831951983156</v>
       </c>
       <c r="E87">
-        <v>65.42</v>
+        <v>66.392</v>
       </c>
       <c r="F87">
-        <v>82.62</v>
+        <v>83.592</v>
       </c>
       <c r="G87">
         <v>0.192</v>
@@ -8421,37 +8421,37 @@
         <v>1.815</v>
       </c>
       <c r="M87">
-        <v>19.481796</v>
+        <v>19.7109936</v>
       </c>
       <c r="N87">
-        <v>-17.66679600000001</v>
+        <v>-17.8959936</v>
       </c>
       <c r="O87">
-        <v>-5.653374720000001</v>
+        <v>-5.726717952000001</v>
       </c>
       <c r="P87">
-        <v>-12.01342128</v>
+        <v>-12.169275648</v>
       </c>
       <c r="Q87">
-        <v>-8.553421280000002</v>
+        <v>-8.709275648000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2959203402148607</v>
+        <v>0.3137860788016364</v>
       </c>
       <c r="T87">
-        <v>3.259906511781811</v>
+        <v>3.492756976909083</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02981244645000901</v>
+        <v>0.02946579009593914</v>
       </c>
       <c r="W87">
-        <v>0.2287702251270879</v>
+        <v>0.2288519666953776</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.0931638951562781</v>
+        <v>0.09208059404980973</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2407427423902538</v>
+        <v>0.2426427423902538</v>
       </c>
       <c r="C88">
-        <v>-64.41680480168441</v>
+        <v>-65.57203772375624</v>
       </c>
       <c r="D88">
-        <v>18.9831951983156</v>
+        <v>18.79996227624376</v>
       </c>
       <c r="E88">
-        <v>66.392</v>
+        <v>67.364</v>
       </c>
       <c r="F88">
-        <v>83.592</v>
+        <v>84.56400000000001</v>
       </c>
       <c r="G88">
         <v>0.192</v>
@@ -8503,37 +8503,37 @@
         <v>1.815</v>
       </c>
       <c r="M88">
-        <v>19.7109936</v>
+        <v>19.9401912</v>
       </c>
       <c r="N88">
-        <v>-17.8959936</v>
+        <v>-18.1251912</v>
       </c>
       <c r="O88">
-        <v>-5.726717952000001</v>
+        <v>-5.800061184000001</v>
       </c>
       <c r="P88">
-        <v>-12.169275648</v>
+        <v>-12.325130016</v>
       </c>
       <c r="Q88">
-        <v>-8.709275648000002</v>
+        <v>-8.865130016000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3137860788016364</v>
+        <v>0.3344003925556085</v>
       </c>
       <c r="T88">
-        <v>3.492756976909083</v>
+        <v>3.761430590517474</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02946579009593914</v>
+        <v>0.02912710285345708</v>
       </c>
       <c r="W88">
-        <v>0.2288519666953776</v>
+        <v>0.2289318291471548</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09208059404980973</v>
+        <v>0.09102219641705334</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2426427423902538</v>
+        <v>0.2445427423902538</v>
       </c>
       <c r="C89">
-        <v>-65.57203772375624</v>
+        <v>-66.72376719661783</v>
       </c>
       <c r="D89">
-        <v>18.79996227624376</v>
+        <v>18.62023280338218</v>
       </c>
       <c r="E89">
-        <v>67.364</v>
+        <v>68.336</v>
       </c>
       <c r="F89">
-        <v>84.56400000000001</v>
+        <v>85.536</v>
       </c>
       <c r="G89">
         <v>0.192</v>
@@ -8585,37 +8585,37 @@
         <v>1.815</v>
       </c>
       <c r="M89">
-        <v>19.9401912</v>
+        <v>20.1693888</v>
       </c>
       <c r="N89">
-        <v>-18.1251912</v>
+        <v>-18.3543888</v>
       </c>
       <c r="O89">
-        <v>-5.800061184000001</v>
+        <v>-5.873404416000001</v>
       </c>
       <c r="P89">
-        <v>-12.325130016</v>
+        <v>-12.480984384</v>
       </c>
       <c r="Q89">
-        <v>-8.865130016000002</v>
+        <v>-9.020984384000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3344003925556085</v>
+        <v>0.358450425268576</v>
       </c>
       <c r="T89">
-        <v>3.761430590517474</v>
+        <v>4.074883139727264</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02912710285345708</v>
+        <v>0.02879611304830416</v>
       </c>
       <c r="W89">
-        <v>0.2289318291471548</v>
+        <v>0.2290098765432099</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09102219641705334</v>
+        <v>0.08998785327595038</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2445427423902538</v>
+        <v>0.2464427423902538</v>
       </c>
       <c r="C90">
-        <v>-66.72376719661783</v>
+        <v>-67.87209274871586</v>
       </c>
       <c r="D90">
-        <v>18.62023280338218</v>
+        <v>18.44390725128414</v>
       </c>
       <c r="E90">
-        <v>68.336</v>
+        <v>69.30800000000001</v>
       </c>
       <c r="F90">
-        <v>85.536</v>
+        <v>86.50800000000001</v>
       </c>
       <c r="G90">
         <v>0.192</v>
@@ -8667,37 +8667,37 @@
         <v>1.815</v>
       </c>
       <c r="M90">
-        <v>20.1693888</v>
+        <v>20.3985864</v>
       </c>
       <c r="N90">
-        <v>-18.3543888</v>
+        <v>-18.5835864</v>
       </c>
       <c r="O90">
-        <v>-5.873404416000001</v>
+        <v>-5.946747648000001</v>
       </c>
       <c r="P90">
-        <v>-12.480984384</v>
+        <v>-12.636838752</v>
       </c>
       <c r="Q90">
-        <v>-9.020984384000002</v>
+        <v>-9.176838752000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.358450425268576</v>
+        <v>0.3868731912020829</v>
       </c>
       <c r="T90">
-        <v>4.074883139727264</v>
+        <v>4.445327061520652</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02879611304830416</v>
+        <v>0.02847256121630074</v>
       </c>
       <c r="W90">
-        <v>0.2290098765432099</v>
+        <v>0.2290861700651963</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08998785327595038</v>
+        <v>0.08897675380093995</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2464427423902538</v>
+        <v>0.2483427423902538</v>
       </c>
       <c r="C91">
-        <v>-67.87209274871586</v>
+        <v>-69.01711017389677</v>
       </c>
       <c r="D91">
-        <v>18.44390725128414</v>
+        <v>18.27088982610324</v>
       </c>
       <c r="E91">
-        <v>69.30800000000001</v>
+        <v>70.28</v>
       </c>
       <c r="F91">
-        <v>86.50800000000001</v>
+        <v>87.48</v>
       </c>
       <c r="G91">
         <v>0.192</v>
@@ -8749,37 +8749,37 @@
         <v>1.815</v>
       </c>
       <c r="M91">
-        <v>20.3985864</v>
+        <v>20.627784</v>
       </c>
       <c r="N91">
-        <v>-18.5835864</v>
+        <v>-18.812784</v>
       </c>
       <c r="O91">
-        <v>-5.946747648000001</v>
+        <v>-6.020090880000001</v>
       </c>
       <c r="P91">
-        <v>-12.636838752</v>
+        <v>-12.79269312</v>
       </c>
       <c r="Q91">
-        <v>-9.176838752000002</v>
+        <v>-9.332693119999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3868731912020829</v>
+        <v>0.4209805103222912</v>
       </c>
       <c r="T91">
-        <v>4.445327061520652</v>
+        <v>4.889859767672718</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02847256121630074</v>
+        <v>0.02815619942500851</v>
       </c>
       <c r="W91">
-        <v>0.2290861700651963</v>
+        <v>0.229160768175583</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08897675380093995</v>
+        <v>0.08798812320315164</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2483427423902538</v>
+        <v>0.2502427423902538</v>
       </c>
       <c r="C92">
-        <v>-69.01711017389677</v>
+        <v>-70.15891170494515</v>
       </c>
       <c r="D92">
-        <v>18.27088982610324</v>
+        <v>18.10108829505486</v>
       </c>
       <c r="E92">
-        <v>70.28</v>
+        <v>71.25200000000001</v>
       </c>
       <c r="F92">
-        <v>87.48</v>
+        <v>88.45200000000001</v>
       </c>
       <c r="G92">
         <v>0.192</v>
@@ -8831,37 +8831,37 @@
         <v>1.815</v>
       </c>
       <c r="M92">
-        <v>20.627784</v>
+        <v>20.8569816</v>
       </c>
       <c r="N92">
-        <v>-18.812784</v>
+        <v>-19.04198160000001</v>
       </c>
       <c r="O92">
-        <v>-6.020090880000001</v>
+        <v>-6.093434112000002</v>
       </c>
       <c r="P92">
-        <v>-12.79269312</v>
+        <v>-12.948547488</v>
       </c>
       <c r="Q92">
-        <v>-9.332693119999998</v>
+        <v>-9.488547488000005</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4209805103222912</v>
+        <v>0.4626672336914347</v>
       </c>
       <c r="T92">
-        <v>4.889859767672718</v>
+        <v>5.433177519636354</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02815619942500851</v>
+        <v>0.02784679064011831</v>
       </c>
       <c r="W92">
-        <v>0.229160768175583</v>
+        <v>0.2292337267670601</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08798812320315164</v>
+        <v>0.08702122075036967</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2502427423902538</v>
+        <v>0.2521427423902538</v>
       </c>
       <c r="C93">
-        <v>-70.15891170494515</v>
+        <v>-71.29758617753482</v>
       </c>
       <c r="D93">
-        <v>18.10108829505486</v>
+        <v>17.93441382246518</v>
       </c>
       <c r="E93">
-        <v>71.25200000000001</v>
+        <v>72.224</v>
       </c>
       <c r="F93">
-        <v>88.45200000000001</v>
+        <v>89.42400000000001</v>
       </c>
       <c r="G93">
         <v>0.192</v>
@@ -8913,37 +8913,37 @@
         <v>1.815</v>
       </c>
       <c r="M93">
-        <v>20.8569816</v>
+        <v>21.0861792</v>
       </c>
       <c r="N93">
-        <v>-19.04198160000001</v>
+        <v>-19.27117920000001</v>
       </c>
       <c r="O93">
-        <v>-6.093434112000002</v>
+        <v>-6.166777344000002</v>
       </c>
       <c r="P93">
-        <v>-12.948547488</v>
+        <v>-13.104401856</v>
       </c>
       <c r="Q93">
-        <v>-9.488547488000005</v>
+        <v>-9.644401856000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4626672336914347</v>
+        <v>0.5147756379028641</v>
       </c>
       <c r="T93">
-        <v>5.433177519636354</v>
+        <v>6.112324709590899</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02784679064011831</v>
+        <v>0.0275441081331605</v>
       </c>
       <c r="W93">
-        <v>0.2292337267670601</v>
+        <v>0.2293050993022007</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08702122075036967</v>
+        <v>0.08607533791612643</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2521427423902538</v>
+        <v>0.2540427423902538</v>
       </c>
       <c r="C94">
-        <v>-71.29758617753482</v>
+        <v>-72.43321918520442</v>
       </c>
       <c r="D94">
-        <v>17.93441382246518</v>
+        <v>17.77078081479558</v>
       </c>
       <c r="E94">
-        <v>72.224</v>
+        <v>73.196</v>
       </c>
       <c r="F94">
-        <v>89.42400000000001</v>
+        <v>90.396</v>
       </c>
       <c r="G94">
         <v>0.192</v>
@@ -8995,37 +8995,37 @@
         <v>1.815</v>
       </c>
       <c r="M94">
-        <v>21.0861792</v>
+        <v>21.3153768</v>
       </c>
       <c r="N94">
-        <v>-19.27117920000001</v>
+        <v>-19.50037680000001</v>
       </c>
       <c r="O94">
-        <v>-6.166777344000002</v>
+        <v>-6.240120576000002</v>
       </c>
       <c r="P94">
-        <v>-13.104401856</v>
+        <v>-13.260256224</v>
       </c>
       <c r="Q94">
-        <v>-9.644401856000002</v>
+        <v>-9.800256224000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5147756379028641</v>
+        <v>0.5817721576032734</v>
       </c>
       <c r="T94">
-        <v>6.112324709590899</v>
+        <v>6.985513953818172</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0275441081331605</v>
+        <v>0.02724793492742759</v>
       </c>
       <c r="W94">
-        <v>0.2293050993022007</v>
+        <v>0.2293749369441126</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08607533791612643</v>
+        <v>0.0851497966482111</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2540427423902538</v>
+        <v>0.2559427423902538</v>
       </c>
       <c r="C95">
-        <v>-72.43321918520442</v>
+        <v>-73.56589322592581</v>
       </c>
       <c r="D95">
-        <v>17.77078081479558</v>
+        <v>17.61010677407421</v>
       </c>
       <c r="E95">
-        <v>73.196</v>
+        <v>74.16800000000001</v>
       </c>
       <c r="F95">
-        <v>90.396</v>
+        <v>91.36800000000001</v>
       </c>
       <c r="G95">
         <v>0.192</v>
@@ -9077,37 +9077,37 @@
         <v>1.815</v>
       </c>
       <c r="M95">
-        <v>21.3153768</v>
+        <v>21.5445744</v>
       </c>
       <c r="N95">
-        <v>-19.50037680000001</v>
+        <v>-19.7295744</v>
       </c>
       <c r="O95">
-        <v>-6.240120576000002</v>
+        <v>-6.313463808000002</v>
       </c>
       <c r="P95">
-        <v>-13.260256224</v>
+        <v>-13.416110592</v>
       </c>
       <c r="Q95">
-        <v>-9.800256224000002</v>
+        <v>-9.956110592000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5817721576032734</v>
+        <v>0.6711008505371524</v>
       </c>
       <c r="T95">
-        <v>6.985513953818172</v>
+        <v>8.149766279454536</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02724793492742759</v>
+        <v>0.02695806327926347</v>
       </c>
       <c r="W95">
-        <v>0.2293749369441126</v>
+        <v>0.2294432886787497</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.0851497966482111</v>
+        <v>0.08424394774769828</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2559427423902538</v>
+        <v>0.2578427423902538</v>
       </c>
       <c r="C96">
-        <v>-73.56589322592581</v>
+        <v>-74.69568784079246</v>
       </c>
       <c r="D96">
-        <v>17.61010677407421</v>
+        <v>17.45231215920754</v>
       </c>
       <c r="E96">
-        <v>74.16800000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F96">
-        <v>91.36800000000001</v>
+        <v>92.34</v>
       </c>
       <c r="G96">
         <v>0.192</v>
@@ -9159,37 +9159,37 @@
         <v>1.815</v>
       </c>
       <c r="M96">
-        <v>21.5445744</v>
+        <v>21.773772</v>
       </c>
       <c r="N96">
-        <v>-19.7295744</v>
+        <v>-19.958772</v>
       </c>
       <c r="O96">
-        <v>-6.313463808000002</v>
+        <v>-6.386807040000001</v>
       </c>
       <c r="P96">
-        <v>-13.416110592</v>
+        <v>-13.57196496</v>
       </c>
       <c r="Q96">
-        <v>-9.956110592000002</v>
+        <v>-10.11196496</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6711008505371524</v>
+        <v>0.7961610206445832</v>
       </c>
       <c r="T96">
-        <v>8.149766279454536</v>
+        <v>9.779719535345446</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02695806327926347</v>
+        <v>0.02667429419211333</v>
       </c>
       <c r="W96">
-        <v>0.2294432886787497</v>
+        <v>0.2295102014294997</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08424394774769828</v>
+        <v>0.08335716935035409</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2578427423902538</v>
+        <v>0.2597427423902539</v>
       </c>
       <c r="C97">
-        <v>-74.69568784079246</v>
+        <v>-75.82267974531807</v>
       </c>
       <c r="D97">
-        <v>17.45231215920754</v>
+        <v>17.29732025468195</v>
       </c>
       <c r="E97">
-        <v>75.14</v>
+        <v>76.11200000000001</v>
       </c>
       <c r="F97">
-        <v>92.34</v>
+        <v>93.31200000000001</v>
       </c>
       <c r="G97">
         <v>0.192</v>
@@ -9241,37 +9241,37 @@
         <v>1.815</v>
       </c>
       <c r="M97">
-        <v>21.773772</v>
+        <v>22.0029696</v>
       </c>
       <c r="N97">
-        <v>-19.958772</v>
+        <v>-20.1879696</v>
       </c>
       <c r="O97">
-        <v>-6.386807040000001</v>
+        <v>-6.460150272000001</v>
       </c>
       <c r="P97">
-        <v>-13.57196496</v>
+        <v>-13.727819328</v>
       </c>
       <c r="Q97">
-        <v>-10.11196496</v>
+        <v>-10.267819328</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7961610206445832</v>
+        <v>0.9837512758057294</v>
       </c>
       <c r="T97">
-        <v>9.779719535345446</v>
+        <v>12.22464941918181</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02667429419211333</v>
+        <v>0.02639643696094548</v>
       </c>
       <c r="W97">
-        <v>0.2295102014294997</v>
+        <v>0.2295757201646091</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08335716935035409</v>
+        <v>0.08248886550295464</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2597427423902538</v>
+        <v>0.2616427423902538</v>
       </c>
       <c r="C98">
-        <v>-75.82267974531804</v>
+        <v>-76.94694295380006</v>
       </c>
       <c r="D98">
-        <v>17.29732025468196</v>
+        <v>17.14505704619994</v>
       </c>
       <c r="E98">
-        <v>76.11199999999999</v>
+        <v>77.084</v>
       </c>
       <c r="F98">
-        <v>93.312</v>
+        <v>94.28400000000001</v>
       </c>
       <c r="G98">
         <v>0.192</v>
@@ -9323,37 +9323,37 @@
         <v>1.815</v>
       </c>
       <c r="M98">
-        <v>22.0029696</v>
+        <v>22.2321672</v>
       </c>
       <c r="N98">
-        <v>-20.1879696</v>
+        <v>-20.4171672</v>
       </c>
       <c r="O98">
-        <v>-6.460150272000001</v>
+        <v>-6.533493504000001</v>
       </c>
       <c r="P98">
-        <v>-13.727819328</v>
+        <v>-13.883673696</v>
       </c>
       <c r="Q98">
-        <v>-10.267819328</v>
+        <v>-10.423673696</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.983751275805727</v>
+        <v>1.296401701074303</v>
       </c>
       <c r="T98">
-        <v>12.22464941918178</v>
+        <v>16.29953255890904</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02639643696094548</v>
+        <v>0.02612430874485326</v>
       </c>
       <c r="W98">
-        <v>0.2295757201646091</v>
+        <v>0.2296398879979636</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08248886550295453</v>
+        <v>0.08163846482766646</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2616427423902538</v>
+        <v>0.2635427423902538</v>
       </c>
       <c r="C99">
-        <v>-76.94694295380006</v>
+        <v>-78.06854889717242</v>
       </c>
       <c r="D99">
-        <v>17.14505704619994</v>
+        <v>16.99545110282758</v>
       </c>
       <c r="E99">
-        <v>77.084</v>
+        <v>78.056</v>
       </c>
       <c r="F99">
-        <v>94.28400000000001</v>
+        <v>95.256</v>
       </c>
       <c r="G99">
         <v>0.192</v>
@@ -9405,37 +9405,37 @@
         <v>1.815</v>
       </c>
       <c r="M99">
-        <v>22.2321672</v>
+        <v>22.4613648</v>
       </c>
       <c r="N99">
-        <v>-20.4171672</v>
+        <v>-20.6463648</v>
       </c>
       <c r="O99">
-        <v>-6.533493504000001</v>
+        <v>-6.606836736</v>
       </c>
       <c r="P99">
-        <v>-13.883673696</v>
+        <v>-14.039528064</v>
       </c>
       <c r="Q99">
-        <v>-10.423673696</v>
+        <v>-10.579528064</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.296401701074303</v>
+        <v>1.921702551611454</v>
       </c>
       <c r="T99">
-        <v>16.29953255890904</v>
+        <v>24.44929883836356</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02612430874485326</v>
+        <v>0.02585773416582415</v>
       </c>
       <c r="W99">
-        <v>0.2296398879979636</v>
+        <v>0.2297027462836987</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.08163846482766646</v>
+        <v>0.08080541926820051</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2635427423902538</v>
+        <v>0.2654427423902538</v>
       </c>
       <c r="C100">
-        <v>-78.06854889717242</v>
+        <v>-79.18756653474135</v>
       </c>
       <c r="D100">
-        <v>16.99545110282758</v>
+        <v>16.84843346525866</v>
       </c>
       <c r="E100">
-        <v>78.056</v>
+        <v>79.02800000000001</v>
       </c>
       <c r="F100">
-        <v>95.256</v>
+        <v>96.22800000000001</v>
       </c>
       <c r="G100">
         <v>0.192</v>
@@ -9487,37 +9487,37 @@
         <v>1.815</v>
       </c>
       <c r="M100">
-        <v>22.4613648</v>
+        <v>22.6905624</v>
       </c>
       <c r="N100">
-        <v>-20.6463648</v>
+        <v>-20.87556240000001</v>
       </c>
       <c r="O100">
-        <v>-6.606836736</v>
+        <v>-6.680179968000003</v>
       </c>
       <c r="P100">
-        <v>-14.039528064</v>
+        <v>-14.195382432</v>
       </c>
       <c r="Q100">
-        <v>-10.579528064</v>
+        <v>-10.73538243200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.921702551611454</v>
+        <v>3.797605103222908</v>
       </c>
       <c r="T100">
-        <v>24.44929883836356</v>
+        <v>48.89859767672713</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02585773416582415</v>
+        <v>0.02559654493182592</v>
       </c>
       <c r="W100">
-        <v>0.2297027462836987</v>
+        <v>0.2297643347050755</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.08080541926820051</v>
+        <v>0.07998920291195588</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2654427423902538</v>
-      </c>
-      <c r="C101">
-        <v>-79.18756653474135</v>
-      </c>
-      <c r="D101">
-        <v>16.84843346525866</v>
-      </c>
-      <c r="E101">
-        <v>79.02800000000001</v>
-      </c>
-      <c r="F101">
-        <v>96.22800000000001</v>
-      </c>
-      <c r="G101">
-        <v>0.192</v>
-      </c>
-      <c r="H101">
-        <v>80</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.274999999999999</v>
-      </c>
-      <c r="K101">
-        <v>3.46</v>
-      </c>
-      <c r="L101">
-        <v>1.815</v>
-      </c>
-      <c r="M101">
-        <v>22.6905624</v>
-      </c>
-      <c r="N101">
-        <v>-20.87556240000001</v>
-      </c>
-      <c r="O101">
-        <v>-6.680179968000003</v>
-      </c>
-      <c r="P101">
-        <v>-14.195382432</v>
-      </c>
-      <c r="Q101">
-        <v>-10.73538243200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.797605103222908</v>
-      </c>
-      <c r="T101">
-        <v>48.89859767672713</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02559654493182592</v>
-      </c>
-      <c r="W101">
-        <v>0.2297643347050755</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07998920291195588</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
